--- a/ER_Summary.xlsx
+++ b/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56252F77-229B-D644-9CEA-602AEFDC50A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FF8C53-FFD1-944F-B36C-78AF77484497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="3" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -20,17 +20,7 @@
     <sheet name="Kabianga" sheetId="4" r:id="rId5"/>
     <sheet name="Kipsigis" sheetId="5" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Summary!$A$5</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Summary!$A$6:$A$45</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Summary!$H$5</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Summary!$H$6:$H$45</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Summary!$A$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Summary!$A$6:$A$45</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Summary!$H$5</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Summary!$H$6:$H$45</definedName>
-  </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -142,12 +132,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -164,6 +148,12 @@
       <color theme="1"/>
       <name val="ArialMT"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -173,40 +163,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -223,22 +185,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -369,7 +326,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -501,124 +458,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>107519.18871700001</c:v>
+                  <c:v>69130.689395195892</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60952.723553999997</c:v>
+                  <c:v>39138.31464429215</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41661.992190999998</c:v>
+                  <c:v>26671.798839738251</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31235.48387</c:v>
+                  <c:v>19902.155268089839</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25405.204740000001</c:v>
+                  <c:v>16090.07288799687</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21987.86335</c:v>
+                  <c:v>13833.705361061368</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19850.655140499999</c:v>
+                  <c:v>12405.245890305207</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18400.840257899999</c:v>
+                  <c:v>11423.537777729693</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17326.582845599998</c:v>
+                  <c:v>10687.827059350577</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>16463.150176199997</c:v>
+                  <c:v>10091.886980842808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15723.137855199999</c:v>
+                  <c:v>9579.218915733265</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15059.898911600001</c:v>
+                  <c:v>9119.5506618533327</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14448.2967128</c:v>
+                  <c:v>8696.4682574837207</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13874.568362400001</c:v>
+                  <c:v>8300.8950618883318</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>13330.979579400002</c:v>
+                  <c:v>7927.6497912172263</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12813.0069281</c:v>
+                  <c:v>7573.6282080551191</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12317.835709300001</c:v>
+                  <c:v>7236.8417605999366</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11843.5781969</c:v>
+                  <c:v>6915.9087544700787</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11388.857311599999</c:v>
+                  <c:v>6609.7845891436154</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10952.578935599999</c:v>
+                  <c:v>6317.618335216921</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10533.824431100002</c:v>
+                  <c:v>6038.676111660634</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>10131.775183899999</c:v>
+                  <c:v>5772.2998072671035</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9745.6832104999994</c:v>
+                  <c:v>5517.8845247170211</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9374.8584357999989</c:v>
+                  <c:v>5274.8659622594105</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9018.6450033000001</c:v>
+                  <c:v>5042.7130882326273</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8676.4313652000001</c:v>
+                  <c:v>4820.9236513839096</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>8347.6261539000006</c:v>
+                  <c:v>4609.0212259922528</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8031.6748525999992</c:v>
+                  <c:v>4406.5531019354157</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7728.0457568999991</c:v>
+                  <c:v>4213.0886528585015</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7436.2299747999996</c:v>
+                  <c:v>4028.2179865461039</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7155.7444976000006</c:v>
+                  <c:v>3851.5507720136238</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>6886.1264967999996</c:v>
+                  <c:v>3682.7151858185371</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>6626.9355176000008</c:v>
+                  <c:v>3521.3569455441375</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6377.7442662000003</c:v>
+                  <c:v>3367.1384119871791</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>6138.1548416999995</c:v>
+                  <c:v>3219.7377488822258</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5907.7772397999997</c:v>
+                  <c:v>3078.8481329323613</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5686.2411976999992</c:v>
+                  <c:v>2944.17700910651</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5473.1948780000002</c:v>
+                  <c:v>2815.44538740798</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5268.3013590999999</c:v>
+                  <c:v>2692.3871780411309</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5071.2324933999998</c:v>
+                  <c:v>2574.7485623724842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,7 +617,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -792,124 +749,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>102417.87455000001</c:v>
+                  <c:v>65907.171375145947</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58061.071605999998</c:v>
+                  <c:v>37313.493037874185</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>39685.954131999999</c:v>
+                  <c:v>25428.49100079012</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>29754.499358000001</c:v>
+                  <c:v>18974.726420700204</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24201.211126000002</c:v>
+                  <c:v>15340.604476309392</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20946.346920399999</c:v>
+                  <c:v>13189.639720471892</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18910.855951999998</c:v>
+                  <c:v>11827.960881081501</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17530.1144494</c:v>
+                  <c:v>10892.184667759273</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16507.085316000001</c:v>
+                  <c:v>10190.919154044586</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15684.855250600001</c:v>
+                  <c:v>9622.89204263188</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14980.170038</c:v>
+                  <c:v>9134.2403385179859</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14348.595240800001</c:v>
+                  <c:v>8696.1044573617419</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13766.186614400001</c:v>
+                  <c:v>8292.8367573642845</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13219.839577600002</c:v>
+                  <c:v>7915.7846974964577</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12702.184976600001</c:v>
+                  <c:v>7560.0093836727738</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12208.9159674</c:v>
+                  <c:v>7222.5520565778424</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11737.350855799999</c:v>
+                  <c:v>6901.5175673190051</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11285.695973399999</c:v>
+                  <c:v>6595.5892820207609</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>10852.636086999999</c:v>
+                  <c:v>6303.771901892429</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10437.133427999999</c:v>
+                  <c:v>6025.254731741793</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10038.311328799999</c:v>
+                  <c:v>5759.3386328798761</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9655.3907096000003</c:v>
+                  <c:v>5505.396671631257</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9287.6622624000011</c:v>
+                  <c:v>5262.8526171154663</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8934.4662844000013</c:v>
+                  <c:v>5031.1689130339437</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8595.1822470000006</c:v>
+                  <c:v>4809.839695341585</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8269.2218417999993</c:v>
+                  <c:v>4598.3865133660747</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7956.0299077999998</c:v>
+                  <c:v>4396.3555140729859</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7655.0742321999996</c:v>
+                  <c:v>4203.3154317977105</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7365.8483320000014</c:v>
+                  <c:v>4018.8560337167028</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7087.8707586</c:v>
+                  <c:v>3842.5868342997146</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6820.6797664000005</c:v>
+                  <c:v>3674.135978187368</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>6563.8363262000003</c:v>
+                  <c:v>3513.149236670446</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>6316.9185619999998</c:v>
+                  <c:v>3359.2890872293419</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6079.524069000001</c:v>
+                  <c:v>3212.2338585267253</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5851.2696818000004</c:v>
+                  <c:v>3071.6769302007042</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5631.7875337999994</c:v>
+                  <c:v>2937.3259805822727</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5420.7248254000006</c:v>
+                  <c:v>2808.90227752176</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5217.7466056000003</c:v>
+                  <c:v>2686.1400087148313</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5022.5278908</c:v>
+                  <c:v>2568.7856485947782</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4834.7638640000005</c:v>
+                  <c:v>2456.5973593167637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -951,7 +908,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -1083,124 +1040,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>40452.364949269002</c:v>
+                  <c:v>30178.507349978001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21280.480682460999</c:v>
+                  <c:v>15842.027898957</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13399.779089423999</c:v>
+                  <c:v>9922.6519113020004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9200.4178535749998</c:v>
+                  <c:v>6748.8770022829995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6905.2993933690004</c:v>
+                  <c:v>4998.0177740284998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5606.5690984914008</c:v>
+                  <c:v>3993.9623541518999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4834.0410343601998</c:v>
+                  <c:v>3386.2099275134001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4342.1927596410997</c:v>
+                  <c:v>2991.4736503197</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4002.1404567677</c:v>
+                  <c:v>2713.3420477982004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3745.9524700441998</c:v>
+                  <c:v>2500.8472547863998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3537.6795635129001</c:v>
+                  <c:v>2326.8909877927999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3358.1901966444002</c:v>
+                  <c:v>2176.9460212734002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3197.2154558811999</c:v>
+                  <c:v>2043.1227216556001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3049.1659390465002</c:v>
+                  <c:v>1921.0451409122998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2910.9260861343</c:v>
+                  <c:v>1808.2036271936001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2780.6974467479999</c:v>
+                  <c:v>1703.0870330058001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2657.3818573952003</c:v>
+                  <c:v>1604.7228104414</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2540.2616700942003</c:v>
+                  <c:v>1512.4343884832001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2428.8283035445002</c:v>
+                  <c:v>1425.7112073230001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2322.6883229732002</c:v>
+                  <c:v>1344.141396689</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2221.5194936791995</c:v>
+                  <c:v>1267.3742104048999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2125.0425840227999</c:v>
+                  <c:v>1195.0987607078</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2033.0053408235999</c:v>
+                  <c:v>1127.0335491909</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1945.1794757394996</c:v>
+                  <c:v>1062.9205967939001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1861.3514278632001</c:v>
+                  <c:v>1002.5214605822</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1781.3218003060999</c:v>
+                  <c:v>945.61203197500004</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1704.903014815</c:v>
+                  <c:v>891.98482971780004</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1631.9191938477998</c:v>
+                  <c:v>841.44542284530007</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1562.2032517741002</c:v>
+                  <c:v>793.81113351409999</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1495.5987423559</c:v>
+                  <c:v>748.91048668929989</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1431.9559410402999</c:v>
+                  <c:v>706.58314463099987</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1371.1337448509998</c:v>
+                  <c:v>666.67834767299996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1312.9994496424001</c:v>
+                  <c:v>629.0545735526</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1257.4260116353003</c:v>
+                  <c:v>593.57875124859993</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1204.2938293840998</c:v>
+                  <c:v>560.1259334138</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1153.4886211394</c:v>
+                  <c:v>528.5783922887</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1104.9025516802001</c:v>
+                  <c:v>498.82596037169998</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1058.4336033843001</c:v>
+                  <c:v>470.7649035869</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1013.9834535909001</c:v>
+                  <c:v>444.29731855990002</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>971.46106474039993</c:v>
+                  <c:v>419.3311195151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1242,7 +1199,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -1374,124 +1331,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>332312.82558446063</c:v>
+                  <c:v>220922.51209236</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>174448.94177935424</c:v>
+                  <c:v>115734.92698060122</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>109277.54037658536</c:v>
+                  <c:v>72129.447754306515</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>74340.037491988376</c:v>
+                  <c:v>48624.917259883296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55070.565181547456</c:v>
+                  <c:v>35559.392377719458</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44023.768124903429</c:v>
+                  <c:v>27990.640845560574</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>37339.956670203588</c:v>
+                  <c:v>23353.587008119888</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33000.857299389223</c:v>
+                  <c:v>20304.641555281007</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29944.880361372416</c:v>
+                  <c:v>18135.353092251749</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>27610.855983306959</c:v>
+                  <c:v>16469.851068282274</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25700.450618235009</c:v>
+                  <c:v>15107.181796076697</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>24053.763575342542</c:v>
+                  <c:v>13938.68055984531</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22583.975516281218</c:v>
+                  <c:v>12904.523176089628</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21242.950112549101</c:v>
+                  <c:v>11970.831069951097</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20003.103556363923</c:v>
+                  <c:v>11117.587937503586</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>18847.83731223645</c:v>
+                  <c:v>10332.252722388883</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17766.482945510197</c:v>
+                  <c:v>9606.3769717712803</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>16751.626113774961</c:v>
+                  <c:v>8933.8080693794327</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>15797.685856665965</c:v>
+                  <c:v>8309.7302674482053</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14900.156686660333</c:v>
+                  <c:v>7730.148783291952</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>14055.200990021849</c:v>
+                  <c:v>7191.6085783035651</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13259.426862837496</c:v>
+                  <c:v>6691.0377610538817</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12509.76435313305</c:v>
+                  <c:v>6225.6574509854827</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11803.394143548758</c:v>
+                  <c:v>5792.9273366916123</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>11137.704375373103</c:v>
+                  <c:v>5390.5106313718989</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10510.26275018114</c:v>
+                  <c:v>5016.2497720125593</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9918.7970831210605</c:v>
+                  <c:v>4668.1482494401416</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9361.1806717177169</c:v>
+                  <c:v>4344.3560940986463</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8835.4205307423181</c:v>
+                  <c:v>4043.1576750325357</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8339.6474368051367</c:v>
+                  <c:v>3762.961070954043</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7872.1072003750023</c:v>
+                  <c:v>3502.288592933146</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7431.1528354821794</c:v>
+                  <c:v>3259.7682101961409</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>7015.2374327279922</c:v>
+                  <c:v>3034.1257237598165</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6622.907614661448</c:v>
+                  <c:v>2824.1775840482123</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>6252.7974928714002</c:v>
+                  <c:v>2628.8242776496541</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5903.6230690654102</c:v>
+                  <c:v>2447.0442255119624</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5574.177035783282</c:v>
+                  <c:v>2277.8881454892271</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5263.3239406504599</c:v>
+                  <c:v>2120.4738391053802</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4969.9956836370629</c:v>
+                  <c:v>1973.981367497471</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4693.1873205393395</c:v>
+                  <c:v>1837.6485851623183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1533,7 +1490,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -1665,124 +1622,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>213660.76020424085</c:v>
+                  <c:v>143908.26359187983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>112174.3783290954</c:v>
+                  <c:v>75395.605915317778</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70287.37143202663</c:v>
+                  <c:v>46998.605152941476</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47839.311661996362</c:v>
+                  <c:v>31695.127169690928</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35463.811067137023</c:v>
+                  <c:v>23190.77614160888</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28373.427324997563</c:v>
+                  <c:v>18266.000827846779</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24086.505476045721</c:v>
+                  <c:v>15249.923095882592</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21305.488038774471</c:v>
+                  <c:v>13267.415549519284</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19347.971162624664</c:v>
+                  <c:v>11857.100214715001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>17853.304665292831</c:v>
+                  <c:v>10774.240842667316</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16629.820706648236</c:v>
+                  <c:v>9888.0329355419435</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15574.843528544037</c:v>
+                  <c:v>9127.7782215874759</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14632.671344331377</c:v>
+                  <c:v>8454.5828156345506</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13772.461112502253</c:v>
+                  <c:v>7846.4445757410786</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12976.573035914125</c:v>
+                  <c:v>7290.3831798686106</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12234.42068035109</c:v>
+                  <c:v>6778.2806528736855</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11539.221914930213</c:v>
+                  <c:v>6304.6787872379546</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10886.279328631041</c:v>
+                  <c:v>5865.6094636200705</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>10272.06757492474</c:v>
+                  <c:v>5457.9706010689051</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9693.746738468104</c:v>
+                  <c:v>5079.190631742089</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9148.9008393998174</c:v>
+                  <c:v>4727.0457788200911</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8635.3954914901096</c:v>
+                  <c:v>4399.558459224364</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8151.2987745436058</c:v>
+                  <c:v>4094.9389331103175</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7694.835778274597</c:v>
+                  <c:v>3811.5501661462727</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7264.3612019957291</c:v>
+                  <c:v>3547.8852936339613</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6858.3417447061101</c:v>
+                  <c:v>3302.552053631689</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6475.3439008420555</c:v>
+                  <c:v>3074.261187522894</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6114.0248269224448</c:v>
+                  <c:v>2861.8171984034093</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5773.125028203619</c:v>
+                  <c:v>2664.1105951015938</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5451.4621882562378</c:v>
+                  <c:v>2480.1111411124903</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5147.9257689168553</c:v>
+                  <c:v>2308.8618363534824</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4861.472170164936</c:v>
+                  <c:v>2149.4734715040236</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4591.1203263998177</c:v>
+                  <c:v>2001.1196552481763</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4335.9476626222977</c:v>
+                  <c:v>1863.0322481115707</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4095.0863598393371</c:v>
+                  <c:v>1734.4971553359032</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>3867.7198936383998</c:v>
+                  <c:v>1614.8504423511949</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>3653.0798183632642</c:v>
+                  <c:v>1503.4747431162552</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3450.4427745991438</c:v>
+                  <c:v>1399.7959361570147</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3259.1277011353677</c:v>
+                  <c:v>1303.2800662797888</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3078.4932349394576</c:v>
+                  <c:v>1213.4304922867395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1813,7 +1770,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2081,7 +2038,7 @@
             <c:numRef>
               <c:f>Summary!$A$6:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
@@ -2213,124 +2170,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>796363.01400497044</c:v>
+                  <c:v>530047.14380455972</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>426917.59595091059</c:v>
+                  <c:v>283424.3684770423</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>274312.63722103596</c:v>
+                  <c:v>181150.99465907837</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>192369.75023555971</c:v>
+                  <c:v>125945.80312064727</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>147046.09150805348</c:v>
+                  <c:v>95178.863657663096</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120937.9748187924</c:v>
+                  <c:v>77273.949109092515</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>105022.0142731095</c:v>
+                  <c:v>66222.926802902584</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>94579.49280510479</c:v>
+                  <c:v>58879.253200608953</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87128.660142364766</c:v>
+                  <c:v>53584.541568160115</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>81358.118545443984</c:v>
+                  <c:v>49459.718189210675</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>76571.258781596145</c:v>
+                  <c:v>46035.564973662687</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>72395.291452930978</c:v>
+                  <c:v>43059.05992192126</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>68628.3456436938</c:v>
+                  <c:v>40391.533728227783</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>65158.985104097854</c:v>
+                  <c:v>37955.000545989264</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>61923.767234412349</c:v>
+                  <c:v>35703.833919455792</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>58884.878334835535</c:v>
+                  <c:v>33609.800672901329</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>56018.27328293561</c:v>
+                  <c:v>31654.137897369576</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>53307.441282800202</c:v>
+                  <c:v>29823.349957973543</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>50740.075133735198</c:v>
+                  <c:v>28106.968566876152</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>48306.30411170164</c:v>
+                  <c:v>26496.353878681752</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45997.757083000863</c:v>
+                  <c:v>24984.043312069065</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>43807.03083185041</c:v>
+                  <c:v>23563.391459884409</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>41727.413941400249</c:v>
+                  <c:v>22228.367075119189</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>39752.734117762855</c:v>
+                  <c:v>20973.432974925137</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>37877.24425553203</c:v>
+                  <c:v>19793.470169162272</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>36095.579502193352</c:v>
+                  <c:v>18683.724022369235</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>34402.700060478113</c:v>
+                  <c:v>17639.771006746076</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>32793.873777287961</c:v>
+                  <c:v>16657.487249080481</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>31264.642899620037</c:v>
+                  <c:v>15733.024090223435</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>29810.809100817274</c:v>
+                  <c:v>14862.78751960165</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>28428.41317433216</c:v>
+                  <c:v>14043.420324118621</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>27113.721573498115</c:v>
+                  <c:v>13271.784451862148</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>25863.211288370214</c:v>
+                  <c:v>12544.945985334072</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>24673.549624119049</c:v>
+                  <c:v>11860.160853922289</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>23541.602205594838</c:v>
+                  <c:v>11214.862045482287</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>22464.396357443213</c:v>
+                  <c:v>10606.647173666492</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>21439.125428926745</c:v>
+                  <c:v>10033.268135605453</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>20463.141802233902</c:v>
+                  <c:v>9492.6200749721065</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>19533.93608826333</c:v>
+                  <c:v>8982.7315789730692</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>18649.137977619197</c:v>
+                  <c:v>8501.7561186534058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2374,7 +2331,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4031,12 +3988,14 @@
   <dimension ref="A3:H48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -4069,1163 +4028,1163 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1">
+      <c r="A6" s="4">
         <v>2026</v>
       </c>
       <c r="B6" s="1">
         <f>Eor!C3 * 0.5</f>
-        <v>107519.18871700001</v>
+        <v>69130.689395195892</v>
       </c>
       <c r="C6" s="1">
         <f>Lanyuak!E3 * 0.5</f>
-        <v>102417.87455000001</v>
+        <v>65907.171375145947</v>
       </c>
       <c r="D6" s="1">
         <f>Mumberes!E3*0.5</f>
-        <v>40452.364949269002</v>
+        <v>30178.507349978001</v>
       </c>
       <c r="E6" s="1">
         <f>Kabianga!C3*0.5</f>
-        <v>332312.82558446063</v>
+        <v>220922.51209236</v>
       </c>
       <c r="F6" s="1">
         <f>Kipsigis!B3*0.5</f>
-        <v>213660.76020424085</v>
+        <v>143908.26359187983</v>
       </c>
       <c r="H6" s="1">
         <f>SUM(B6:F6)</f>
-        <v>796363.01400497044</v>
+        <v>530047.14380455972</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1">
+      <c r="A7" s="4">
         <v>2027</v>
       </c>
       <c r="B7" s="1">
         <f>Eor!C4 * 0.5</f>
-        <v>60952.723553999997</v>
+        <v>39138.31464429215</v>
       </c>
       <c r="C7" s="1">
         <f>Lanyuak!E4 * 0.5</f>
-        <v>58061.071605999998</v>
+        <v>37313.493037874185</v>
       </c>
       <c r="D7" s="1">
         <f>Mumberes!E4*0.5</f>
-        <v>21280.480682460999</v>
+        <v>15842.027898957</v>
       </c>
       <c r="E7" s="1">
         <f>Kabianga!C4*0.5</f>
-        <v>174448.94177935424</v>
+        <v>115734.92698060122</v>
       </c>
       <c r="F7" s="1">
         <f>Kipsigis!B4*0.5</f>
-        <v>112174.3783290954</v>
+        <v>75395.605915317778</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H45" si="0">SUM(B7:F7)</f>
-        <v>426917.59595091059</v>
+        <v>283424.3684770423</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1">
+      <c r="A8" s="4">
         <v>2028</v>
       </c>
       <c r="B8" s="1">
         <f>Eor!C5 * 0.5</f>
-        <v>41661.992190999998</v>
+        <v>26671.798839738251</v>
       </c>
       <c r="C8" s="1">
         <f>Lanyuak!E5 * 0.5</f>
-        <v>39685.954131999999</v>
+        <v>25428.49100079012</v>
       </c>
       <c r="D8" s="1">
         <f>Mumberes!E5*0.5</f>
-        <v>13399.779089423999</v>
+        <v>9922.6519113020004</v>
       </c>
       <c r="E8" s="1">
         <f>Kabianga!C5*0.5</f>
-        <v>109277.54037658536</v>
+        <v>72129.447754306515</v>
       </c>
       <c r="F8" s="1">
         <f>Kipsigis!B5*0.5</f>
-        <v>70287.37143202663</v>
+        <v>46998.605152941476</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>274312.63722103596</v>
+        <v>181150.99465907837</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="1">
+      <c r="A9" s="4">
         <v>2029</v>
       </c>
       <c r="B9" s="1">
         <f>Eor!C6 * 0.5</f>
-        <v>31235.48387</v>
+        <v>19902.155268089839</v>
       </c>
       <c r="C9" s="1">
         <f>Lanyuak!E6 * 0.5</f>
-        <v>29754.499358000001</v>
+        <v>18974.726420700204</v>
       </c>
       <c r="D9" s="1">
         <f>Mumberes!E6*0.5</f>
-        <v>9200.4178535749998</v>
+        <v>6748.8770022829995</v>
       </c>
       <c r="E9" s="1">
         <f>Kabianga!C6*0.5</f>
-        <v>74340.037491988376</v>
+        <v>48624.917259883296</v>
       </c>
       <c r="F9" s="1">
         <f>Kipsigis!B6*0.5</f>
-        <v>47839.311661996362</v>
+        <v>31695.127169690928</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>192369.75023555971</v>
+        <v>125945.80312064727</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1">
+      <c r="A10" s="4">
         <v>2030</v>
       </c>
       <c r="B10" s="1">
         <f>Eor!C7 * 0.5</f>
-        <v>25405.204740000001</v>
+        <v>16090.07288799687</v>
       </c>
       <c r="C10" s="1">
         <f>Lanyuak!E7 * 0.5</f>
-        <v>24201.211126000002</v>
+        <v>15340.604476309392</v>
       </c>
       <c r="D10" s="1">
         <f>Mumberes!E7*0.5</f>
-        <v>6905.2993933690004</v>
+        <v>4998.0177740284998</v>
       </c>
       <c r="E10" s="1">
         <f>Kabianga!C7*0.5</f>
-        <v>55070.565181547456</v>
+        <v>35559.392377719458</v>
       </c>
       <c r="F10" s="1">
         <f>Kipsigis!B7*0.5</f>
-        <v>35463.811067137023</v>
+        <v>23190.77614160888</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>147046.09150805348</v>
+        <v>95178.863657663096</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1">
+      <c r="A11" s="4">
         <v>2031</v>
       </c>
       <c r="B11" s="1">
         <f>Eor!C8 * 0.5</f>
-        <v>21987.86335</v>
+        <v>13833.705361061368</v>
       </c>
       <c r="C11" s="1">
         <f>Lanyuak!E8 * 0.5</f>
-        <v>20946.346920399999</v>
+        <v>13189.639720471892</v>
       </c>
       <c r="D11" s="1">
         <f>Mumberes!E8*0.5</f>
-        <v>5606.5690984914008</v>
+        <v>3993.9623541518999</v>
       </c>
       <c r="E11" s="1">
         <f>Kabianga!C8*0.5</f>
-        <v>44023.768124903429</v>
+        <v>27990.640845560574</v>
       </c>
       <c r="F11" s="1">
         <f>Kipsigis!B8*0.5</f>
-        <v>28373.427324997563</v>
+        <v>18266.000827846779</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
-        <v>120937.9748187924</v>
+        <v>77273.949109092515</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1">
+      <c r="A12" s="4">
         <v>2032</v>
       </c>
       <c r="B12" s="1">
         <f>Eor!C9 * 0.5</f>
-        <v>19850.655140499999</v>
+        <v>12405.245890305207</v>
       </c>
       <c r="C12" s="1">
         <f>Lanyuak!E9 * 0.5</f>
-        <v>18910.855951999998</v>
+        <v>11827.960881081501</v>
       </c>
       <c r="D12" s="1">
         <f>Mumberes!E9*0.5</f>
-        <v>4834.0410343601998</v>
+        <v>3386.2099275134001</v>
       </c>
       <c r="E12" s="1">
         <f>Kabianga!C9*0.5</f>
-        <v>37339.956670203588</v>
+        <v>23353.587008119888</v>
       </c>
       <c r="F12" s="1">
         <f>Kipsigis!B9*0.5</f>
-        <v>24086.505476045721</v>
+        <v>15249.923095882592</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
-        <v>105022.0142731095</v>
+        <v>66222.926802902584</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1">
+      <c r="A13" s="4">
         <v>2033</v>
       </c>
       <c r="B13" s="1">
         <f>Eor!C10 * 0.5</f>
-        <v>18400.840257899999</v>
+        <v>11423.537777729693</v>
       </c>
       <c r="C13" s="1">
         <f>Lanyuak!E10 * 0.5</f>
-        <v>17530.1144494</v>
+        <v>10892.184667759273</v>
       </c>
       <c r="D13" s="1">
         <f>Mumberes!E10*0.5</f>
-        <v>4342.1927596410997</v>
+        <v>2991.4736503197</v>
       </c>
       <c r="E13" s="1">
         <f>Kabianga!C10*0.5</f>
-        <v>33000.857299389223</v>
+        <v>20304.641555281007</v>
       </c>
       <c r="F13" s="1">
         <f>Kipsigis!B10*0.5</f>
-        <v>21305.488038774471</v>
+        <v>13267.415549519284</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
-        <v>94579.49280510479</v>
+        <v>58879.253200608953</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1">
+      <c r="A14" s="4">
         <v>2034</v>
       </c>
       <c r="B14" s="1">
         <f>Eor!C11 * 0.5</f>
-        <v>17326.582845599998</v>
+        <v>10687.827059350577</v>
       </c>
       <c r="C14" s="1">
         <f>Lanyuak!E11 * 0.5</f>
-        <v>16507.085316000001</v>
+        <v>10190.919154044586</v>
       </c>
       <c r="D14" s="1">
         <f>Mumberes!E11*0.5</f>
-        <v>4002.1404567677</v>
+        <v>2713.3420477982004</v>
       </c>
       <c r="E14" s="1">
         <f>Kabianga!C11*0.5</f>
-        <v>29944.880361372416</v>
+        <v>18135.353092251749</v>
       </c>
       <c r="F14" s="1">
         <f>Kipsigis!B11*0.5</f>
-        <v>19347.971162624664</v>
+        <v>11857.100214715001</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
-        <v>87128.660142364766</v>
+        <v>53584.541568160115</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1">
+      <c r="A15" s="4">
         <v>2035</v>
       </c>
       <c r="B15" s="1">
         <f>Eor!C12 * 0.5</f>
-        <v>16463.150176199997</v>
+        <v>10091.886980842808</v>
       </c>
       <c r="C15" s="1">
         <f>Lanyuak!E12 * 0.5</f>
-        <v>15684.855250600001</v>
+        <v>9622.89204263188</v>
       </c>
       <c r="D15" s="1">
         <f>Mumberes!E12*0.5</f>
-        <v>3745.9524700441998</v>
+        <v>2500.8472547863998</v>
       </c>
       <c r="E15" s="1">
         <f>Kabianga!C12*0.5</f>
-        <v>27610.855983306959</v>
+        <v>16469.851068282274</v>
       </c>
       <c r="F15" s="1">
         <f>Kipsigis!B12*0.5</f>
-        <v>17853.304665292831</v>
+        <v>10774.240842667316</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
-        <v>81358.118545443984</v>
+        <v>49459.718189210675</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1">
+      <c r="A16" s="4">
         <v>2036</v>
       </c>
       <c r="B16" s="1">
         <f>Eor!C13 * 0.5</f>
-        <v>15723.137855199999</v>
+        <v>9579.218915733265</v>
       </c>
       <c r="C16" s="1">
         <f>Lanyuak!E13 * 0.5</f>
-        <v>14980.170038</v>
+        <v>9134.2403385179859</v>
       </c>
       <c r="D16" s="1">
         <f>Mumberes!E13*0.5</f>
-        <v>3537.6795635129001</v>
+        <v>2326.8909877927999</v>
       </c>
       <c r="E16" s="1">
         <f>Kabianga!C13*0.5</f>
-        <v>25700.450618235009</v>
+        <v>15107.181796076697</v>
       </c>
       <c r="F16" s="1">
         <f>Kipsigis!B13*0.5</f>
-        <v>16629.820706648236</v>
+        <v>9888.0329355419435</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
-        <v>76571.258781596145</v>
+        <v>46035.564973662687</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="1">
+      <c r="A17" s="4">
         <v>2037</v>
       </c>
       <c r="B17" s="1">
         <f>Eor!C14 * 0.5</f>
-        <v>15059.898911600001</v>
+        <v>9119.5506618533327</v>
       </c>
       <c r="C17" s="1">
         <f>Lanyuak!E14 * 0.5</f>
-        <v>14348.595240800001</v>
+        <v>8696.1044573617419</v>
       </c>
       <c r="D17" s="1">
         <f>Mumberes!E14*0.5</f>
-        <v>3358.1901966444002</v>
+        <v>2176.9460212734002</v>
       </c>
       <c r="E17" s="1">
         <f>Kabianga!C14*0.5</f>
-        <v>24053.763575342542</v>
+        <v>13938.68055984531</v>
       </c>
       <c r="F17" s="1">
         <f>Kipsigis!B14*0.5</f>
-        <v>15574.843528544037</v>
+        <v>9127.7782215874759</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
-        <v>72395.291452930978</v>
+        <v>43059.05992192126</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="1">
+      <c r="A18" s="4">
         <v>2038</v>
       </c>
       <c r="B18" s="1">
         <f>Eor!C15 * 0.5</f>
-        <v>14448.2967128</v>
+        <v>8696.4682574837207</v>
       </c>
       <c r="C18" s="1">
         <f>Lanyuak!E15 * 0.5</f>
-        <v>13766.186614400001</v>
+        <v>8292.8367573642845</v>
       </c>
       <c r="D18" s="1">
         <f>Mumberes!E15*0.5</f>
-        <v>3197.2154558811999</v>
+        <v>2043.1227216556001</v>
       </c>
       <c r="E18" s="1">
         <f>Kabianga!C15*0.5</f>
-        <v>22583.975516281218</v>
+        <v>12904.523176089628</v>
       </c>
       <c r="F18" s="1">
         <f>Kipsigis!B15*0.5</f>
-        <v>14632.671344331377</v>
+        <v>8454.5828156345506</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
-        <v>68628.3456436938</v>
+        <v>40391.533728227783</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="1">
+      <c r="A19" s="4">
         <v>2039</v>
       </c>
       <c r="B19" s="1">
         <f>Eor!C16 * 0.5</f>
-        <v>13874.568362400001</v>
+        <v>8300.8950618883318</v>
       </c>
       <c r="C19" s="1">
         <f>Lanyuak!E16 * 0.5</f>
-        <v>13219.839577600002</v>
+        <v>7915.7846974964577</v>
       </c>
       <c r="D19" s="1">
         <f>Mumberes!E16*0.5</f>
-        <v>3049.1659390465002</v>
+        <v>1921.0451409122998</v>
       </c>
       <c r="E19" s="1">
         <f>Kabianga!C16*0.5</f>
-        <v>21242.950112549101</v>
+        <v>11970.831069951097</v>
       </c>
       <c r="F19" s="1">
         <f>Kipsigis!B16*0.5</f>
-        <v>13772.461112502253</v>
+        <v>7846.4445757410786</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
-        <v>65158.985104097854</v>
+        <v>37955.000545989264</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="1">
+      <c r="A20" s="4">
         <v>2040</v>
       </c>
       <c r="B20" s="1">
         <f>Eor!C17 * 0.5</f>
-        <v>13330.979579400002</v>
+        <v>7927.6497912172263</v>
       </c>
       <c r="C20" s="1">
         <f>Lanyuak!E17 * 0.5</f>
-        <v>12702.184976600001</v>
+        <v>7560.0093836727738</v>
       </c>
       <c r="D20" s="1">
         <f>Mumberes!E17*0.5</f>
-        <v>2910.9260861343</v>
+        <v>1808.2036271936001</v>
       </c>
       <c r="E20" s="1">
         <f>Kabianga!C17*0.5</f>
-        <v>20003.103556363923</v>
+        <v>11117.587937503586</v>
       </c>
       <c r="F20" s="1">
         <f>Kipsigis!B17*0.5</f>
-        <v>12976.573035914125</v>
+        <v>7290.3831798686106</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
-        <v>61923.767234412349</v>
+        <v>35703.833919455792</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="1">
+      <c r="A21" s="4">
         <v>2041</v>
       </c>
       <c r="B21" s="1">
         <f>Eor!C18 * 0.5</f>
-        <v>12813.0069281</v>
+        <v>7573.6282080551191</v>
       </c>
       <c r="C21" s="1">
         <f>Lanyuak!E18 * 0.5</f>
-        <v>12208.9159674</v>
+        <v>7222.5520565778424</v>
       </c>
       <c r="D21" s="1">
         <f>Mumberes!E18*0.5</f>
-        <v>2780.6974467479999</v>
+        <v>1703.0870330058001</v>
       </c>
       <c r="E21" s="1">
         <f>Kabianga!C18*0.5</f>
-        <v>18847.83731223645</v>
+        <v>10332.252722388883</v>
       </c>
       <c r="F21" s="1">
         <f>Kipsigis!B18*0.5</f>
-        <v>12234.42068035109</v>
+        <v>6778.2806528736855</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
-        <v>58884.878334835535</v>
+        <v>33609.800672901329</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="1">
+      <c r="A22" s="4">
         <v>2042</v>
       </c>
       <c r="B22" s="1">
         <f>Eor!C19 * 0.5</f>
-        <v>12317.835709300001</v>
+        <v>7236.8417605999366</v>
       </c>
       <c r="C22" s="1">
         <f>Lanyuak!E19 * 0.5</f>
-        <v>11737.350855799999</v>
+        <v>6901.5175673190051</v>
       </c>
       <c r="D22" s="1">
         <f>Mumberes!E19*0.5</f>
-        <v>2657.3818573952003</v>
+        <v>1604.7228104414</v>
       </c>
       <c r="E22" s="1">
         <f>Kabianga!C19*0.5</f>
-        <v>17766.482945510197</v>
+        <v>9606.3769717712803</v>
       </c>
       <c r="F22" s="1">
         <f>Kipsigis!B19*0.5</f>
-        <v>11539.221914930213</v>
+        <v>6304.6787872379546</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
-        <v>56018.27328293561</v>
+        <v>31654.137897369576</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="1">
+      <c r="A23" s="4">
         <v>2043</v>
       </c>
       <c r="B23" s="1">
         <f>Eor!C20 * 0.5</f>
-        <v>11843.5781969</v>
+        <v>6915.9087544700787</v>
       </c>
       <c r="C23" s="1">
         <f>Lanyuak!E20 * 0.5</f>
-        <v>11285.695973399999</v>
+        <v>6595.5892820207609</v>
       </c>
       <c r="D23" s="1">
         <f>Mumberes!E20*0.5</f>
-        <v>2540.2616700942003</v>
+        <v>1512.4343884832001</v>
       </c>
       <c r="E23" s="1">
         <f>Kabianga!C20*0.5</f>
-        <v>16751.626113774961</v>
+        <v>8933.8080693794327</v>
       </c>
       <c r="F23" s="1">
         <f>Kipsigis!B20*0.5</f>
-        <v>10886.279328631041</v>
+        <v>5865.6094636200705</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
-        <v>53307.441282800202</v>
+        <v>29823.349957973543</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="1">
+      <c r="A24" s="4">
         <v>2044</v>
       </c>
       <c r="B24" s="1">
         <f>Eor!C21 * 0.5</f>
-        <v>11388.857311599999</v>
+        <v>6609.7845891436154</v>
       </c>
       <c r="C24" s="1">
         <f>Lanyuak!E21 * 0.5</f>
-        <v>10852.636086999999</v>
+        <v>6303.771901892429</v>
       </c>
       <c r="D24" s="1">
         <f>Mumberes!E21*0.5</f>
-        <v>2428.8283035445002</v>
+        <v>1425.7112073230001</v>
       </c>
       <c r="E24" s="1">
         <f>Kabianga!C21*0.5</f>
-        <v>15797.685856665965</v>
+        <v>8309.7302674482053</v>
       </c>
       <c r="F24" s="1">
         <f>Kipsigis!B21*0.5</f>
-        <v>10272.06757492474</v>
+        <v>5457.9706010689051</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
-        <v>50740.075133735198</v>
+        <v>28106.968566876152</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="1">
+      <c r="A25" s="4">
         <v>2045</v>
       </c>
       <c r="B25" s="1">
         <f>Eor!C22 * 0.5</f>
-        <v>10952.578935599999</v>
+        <v>6317.618335216921</v>
       </c>
       <c r="C25" s="1">
         <f>Lanyuak!E22 * 0.5</f>
-        <v>10437.133427999999</v>
+        <v>6025.254731741793</v>
       </c>
       <c r="D25" s="1">
         <f>Mumberes!E22*0.5</f>
-        <v>2322.6883229732002</v>
+        <v>1344.141396689</v>
       </c>
       <c r="E25" s="1">
         <f>Kabianga!C22*0.5</f>
-        <v>14900.156686660333</v>
+        <v>7730.148783291952</v>
       </c>
       <c r="F25" s="1">
         <f>Kipsigis!B22*0.5</f>
-        <v>9693.746738468104</v>
+        <v>5079.190631742089</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
-        <v>48306.30411170164</v>
+        <v>26496.353878681752</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="1">
+      <c r="A26" s="4">
         <v>2046</v>
       </c>
       <c r="B26" s="1">
         <f>Eor!C23 * 0.5</f>
-        <v>10533.824431100002</v>
+        <v>6038.676111660634</v>
       </c>
       <c r="C26" s="1">
         <f>Lanyuak!E23 * 0.5</f>
-        <v>10038.311328799999</v>
+        <v>5759.3386328798761</v>
       </c>
       <c r="D26" s="1">
         <f>Mumberes!E23*0.5</f>
-        <v>2221.5194936791995</v>
+        <v>1267.3742104048999</v>
       </c>
       <c r="E26" s="1">
         <f>Kabianga!C23*0.5</f>
-        <v>14055.200990021849</v>
+        <v>7191.6085783035651</v>
       </c>
       <c r="F26" s="1">
         <f>Kipsigis!B23*0.5</f>
-        <v>9148.9008393998174</v>
+        <v>4727.0457788200911</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
-        <v>45997.757083000863</v>
+        <v>24984.043312069065</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="1">
+      <c r="A27" s="4">
         <v>2047</v>
       </c>
       <c r="B27" s="1">
         <f>Eor!C24 * 0.5</f>
-        <v>10131.775183899999</v>
+        <v>5772.2998072671035</v>
       </c>
       <c r="C27" s="1">
         <f>Lanyuak!E24 * 0.5</f>
-        <v>9655.3907096000003</v>
+        <v>5505.396671631257</v>
       </c>
       <c r="D27" s="1">
         <f>Mumberes!E24*0.5</f>
-        <v>2125.0425840227999</v>
+        <v>1195.0987607078</v>
       </c>
       <c r="E27" s="1">
         <f>Kabianga!C24*0.5</f>
-        <v>13259.426862837496</v>
+        <v>6691.0377610538817</v>
       </c>
       <c r="F27" s="1">
         <f>Kipsigis!B24*0.5</f>
-        <v>8635.3954914901096</v>
+        <v>4399.558459224364</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="0"/>
-        <v>43807.03083185041</v>
+        <v>23563.391459884409</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="1">
+      <c r="A28" s="4">
         <v>2048</v>
       </c>
       <c r="B28" s="1">
         <f>Eor!C25 * 0.5</f>
-        <v>9745.6832104999994</v>
+        <v>5517.8845247170211</v>
       </c>
       <c r="C28" s="1">
         <f>Lanyuak!E25 * 0.5</f>
-        <v>9287.6622624000011</v>
+        <v>5262.8526171154663</v>
       </c>
       <c r="D28" s="1">
         <f>Mumberes!E25*0.5</f>
-        <v>2033.0053408235999</v>
+        <v>1127.0335491909</v>
       </c>
       <c r="E28" s="1">
         <f>Kabianga!C25*0.5</f>
-        <v>12509.76435313305</v>
+        <v>6225.6574509854827</v>
       </c>
       <c r="F28" s="1">
         <f>Kipsigis!B25*0.5</f>
-        <v>8151.2987745436058</v>
+        <v>4094.9389331103175</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
-        <v>41727.413941400249</v>
+        <v>22228.367075119189</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="1">
+      <c r="A29" s="4">
         <v>2049</v>
       </c>
       <c r="B29" s="1">
         <f>Eor!C26 * 0.5</f>
-        <v>9374.8584357999989</v>
+        <v>5274.8659622594105</v>
       </c>
       <c r="C29" s="1">
         <f>Lanyuak!E26 * 0.5</f>
-        <v>8934.4662844000013</v>
+        <v>5031.1689130339437</v>
       </c>
       <c r="D29" s="1">
         <f>Mumberes!E26*0.5</f>
-        <v>1945.1794757394996</v>
+        <v>1062.9205967939001</v>
       </c>
       <c r="E29" s="1">
         <f>Kabianga!C26*0.5</f>
-        <v>11803.394143548758</v>
+        <v>5792.9273366916123</v>
       </c>
       <c r="F29" s="1">
         <f>Kipsigis!B26*0.5</f>
-        <v>7694.835778274597</v>
+        <v>3811.5501661462727</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="0"/>
-        <v>39752.734117762855</v>
+        <v>20973.432974925137</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="1">
+      <c r="A30" s="4">
         <v>2050</v>
       </c>
       <c r="B30" s="1">
         <f>Eor!C27 * 0.5</f>
-        <v>9018.6450033000001</v>
+        <v>5042.7130882326273</v>
       </c>
       <c r="C30" s="1">
         <f>Lanyuak!E27 * 0.5</f>
-        <v>8595.1822470000006</v>
+        <v>4809.839695341585</v>
       </c>
       <c r="D30" s="1">
         <f>Mumberes!E27*0.5</f>
-        <v>1861.3514278632001</v>
+        <v>1002.5214605822</v>
       </c>
       <c r="E30" s="1">
         <f>Kabianga!C27*0.5</f>
-        <v>11137.704375373103</v>
+        <v>5390.5106313718989</v>
       </c>
       <c r="F30" s="1">
         <f>Kipsigis!B27*0.5</f>
-        <v>7264.3612019957291</v>
+        <v>3547.8852936339613</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="0"/>
-        <v>37877.24425553203</v>
+        <v>19793.470169162272</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="1">
+      <c r="A31" s="4">
         <v>2051</v>
       </c>
       <c r="B31" s="1">
         <f>Eor!C28 * 0.5</f>
-        <v>8676.4313652000001</v>
+        <v>4820.9236513839096</v>
       </c>
       <c r="C31" s="1">
         <f>Lanyuak!E28 * 0.5</f>
-        <v>8269.2218417999993</v>
+        <v>4598.3865133660747</v>
       </c>
       <c r="D31" s="1">
         <f>Mumberes!E28*0.5</f>
-        <v>1781.3218003060999</v>
+        <v>945.61203197500004</v>
       </c>
       <c r="E31" s="1">
         <f>Kabianga!C28*0.5</f>
-        <v>10510.26275018114</v>
+        <v>5016.2497720125593</v>
       </c>
       <c r="F31" s="1">
         <f>Kipsigis!B28*0.5</f>
-        <v>6858.3417447061101</v>
+        <v>3302.552053631689</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="0"/>
-        <v>36095.579502193352</v>
+        <v>18683.724022369235</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="1">
+      <c r="A32" s="4">
         <v>2052</v>
       </c>
       <c r="B32" s="1">
         <f>Eor!C29 * 0.5</f>
-        <v>8347.6261539000006</v>
+        <v>4609.0212259922528</v>
       </c>
       <c r="C32" s="1">
         <f>Lanyuak!E29 * 0.5</f>
-        <v>7956.0299077999998</v>
+        <v>4396.3555140729859</v>
       </c>
       <c r="D32" s="1">
         <f>Mumberes!E29*0.5</f>
-        <v>1704.903014815</v>
+        <v>891.98482971780004</v>
       </c>
       <c r="E32" s="1">
         <f>Kabianga!C29*0.5</f>
-        <v>9918.7970831210605</v>
+        <v>4668.1482494401416</v>
       </c>
       <c r="F32" s="1">
         <f>Kipsigis!B29*0.5</f>
-        <v>6475.3439008420555</v>
+        <v>3074.261187522894</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="0"/>
-        <v>34402.700060478113</v>
+        <v>17639.771006746076</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="1">
+      <c r="A33" s="4">
         <v>2053</v>
       </c>
       <c r="B33" s="1">
         <f>Eor!C30 * 0.5</f>
-        <v>8031.6748525999992</v>
+        <v>4406.5531019354157</v>
       </c>
       <c r="C33" s="1">
         <f>Lanyuak!E30 * 0.5</f>
-        <v>7655.0742321999996</v>
+        <v>4203.3154317977105</v>
       </c>
       <c r="D33" s="1">
         <f>Mumberes!E30*0.5</f>
-        <v>1631.9191938477998</v>
+        <v>841.44542284530007</v>
       </c>
       <c r="E33" s="1">
         <f>Kabianga!C30*0.5</f>
-        <v>9361.1806717177169</v>
+        <v>4344.3560940986463</v>
       </c>
       <c r="F33" s="1">
         <f>Kipsigis!B30*0.5</f>
-        <v>6114.0248269224448</v>
+        <v>2861.8171984034093</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="0"/>
-        <v>32793.873777287961</v>
+        <v>16657.487249080481</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="1">
+      <c r="A34" s="4">
         <v>2054</v>
       </c>
       <c r="B34" s="1">
         <f>Eor!C31 * 0.5</f>
-        <v>7728.0457568999991</v>
+        <v>4213.0886528585015</v>
       </c>
       <c r="C34" s="1">
         <f>Lanyuak!E31 * 0.5</f>
-        <v>7365.8483320000014</v>
+        <v>4018.8560337167028</v>
       </c>
       <c r="D34" s="1">
         <f>Mumberes!E31*0.5</f>
-        <v>1562.2032517741002</v>
+        <v>793.81113351409999</v>
       </c>
       <c r="E34" s="1">
         <f>Kabianga!C31*0.5</f>
-        <v>8835.4205307423181</v>
+        <v>4043.1576750325357</v>
       </c>
       <c r="F34" s="1">
         <f>Kipsigis!B31*0.5</f>
-        <v>5773.125028203619</v>
+        <v>2664.1105951015938</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="0"/>
-        <v>31264.642899620037</v>
+        <v>15733.024090223435</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="1">
+      <c r="A35" s="4">
         <v>2055</v>
       </c>
       <c r="B35" s="1">
         <f>Eor!C32 * 0.5</f>
-        <v>7436.2299747999996</v>
+        <v>4028.2179865461039</v>
       </c>
       <c r="C35" s="1">
         <f>Lanyuak!E32 * 0.5</f>
-        <v>7087.8707586</v>
+        <v>3842.5868342997146</v>
       </c>
       <c r="D35" s="1">
         <f>Mumberes!E32*0.5</f>
-        <v>1495.5987423559</v>
+        <v>748.91048668929989</v>
       </c>
       <c r="E35" s="1">
         <f>Kabianga!C32*0.5</f>
-        <v>8339.6474368051367</v>
+        <v>3762.961070954043</v>
       </c>
       <c r="F35" s="1">
         <f>Kipsigis!B32*0.5</f>
-        <v>5451.4621882562378</v>
+        <v>2480.1111411124903</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="0"/>
-        <v>29810.809100817274</v>
+        <v>14862.78751960165</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="1">
+      <c r="A36" s="4">
         <v>2056</v>
       </c>
       <c r="B36" s="1">
         <f>Eor!C33 * 0.5</f>
-        <v>7155.7444976000006</v>
+        <v>3851.5507720136238</v>
       </c>
       <c r="C36" s="1">
         <f>Lanyuak!E33 * 0.5</f>
-        <v>6820.6797664000005</v>
+        <v>3674.135978187368</v>
       </c>
       <c r="D36" s="1">
         <f>Mumberes!E33*0.5</f>
-        <v>1431.9559410402999</v>
+        <v>706.58314463099987</v>
       </c>
       <c r="E36" s="1">
         <f>Kabianga!C33*0.5</f>
-        <v>7872.1072003750023</v>
+        <v>3502.288592933146</v>
       </c>
       <c r="F36" s="1">
         <f>Kipsigis!B33*0.5</f>
-        <v>5147.9257689168553</v>
+        <v>2308.8618363534824</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="0"/>
-        <v>28428.41317433216</v>
+        <v>14043.420324118621</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="1">
+      <c r="A37" s="4">
         <v>2057</v>
       </c>
       <c r="B37" s="1">
         <f>Eor!C34 * 0.5</f>
-        <v>6886.1264967999996</v>
+        <v>3682.7151858185371</v>
       </c>
       <c r="C37" s="1">
         <f>Lanyuak!E34 * 0.5</f>
-        <v>6563.8363262000003</v>
+        <v>3513.149236670446</v>
       </c>
       <c r="D37" s="1">
         <f>Mumberes!E34*0.5</f>
-        <v>1371.1337448509998</v>
+        <v>666.67834767299996</v>
       </c>
       <c r="E37" s="1">
         <f>Kabianga!C34*0.5</f>
-        <v>7431.1528354821794</v>
+        <v>3259.7682101961409</v>
       </c>
       <c r="F37" s="1">
         <f>Kipsigis!B34*0.5</f>
-        <v>4861.472170164936</v>
+        <v>2149.4734715040236</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="0"/>
-        <v>27113.721573498115</v>
+        <v>13271.784451862148</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="1">
+      <c r="A38" s="4">
         <v>2058</v>
       </c>
       <c r="B38" s="1">
         <f>Eor!C35 * 0.5</f>
-        <v>6626.9355176000008</v>
+        <v>3521.3569455441375</v>
       </c>
       <c r="C38" s="1">
         <f>Lanyuak!E35 * 0.5</f>
-        <v>6316.9185619999998</v>
+        <v>3359.2890872293419</v>
       </c>
       <c r="D38" s="1">
         <f>Mumberes!E35*0.5</f>
-        <v>1312.9994496424001</v>
+        <v>629.0545735526</v>
       </c>
       <c r="E38" s="1">
         <f>Kabianga!C35*0.5</f>
-        <v>7015.2374327279922</v>
+        <v>3034.1257237598165</v>
       </c>
       <c r="F38" s="1">
         <f>Kipsigis!B35*0.5</f>
-        <v>4591.1203263998177</v>
+        <v>2001.1196552481763</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="0"/>
-        <v>25863.211288370214</v>
+        <v>12544.945985334072</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="1">
+      <c r="A39" s="4">
         <v>2059</v>
       </c>
       <c r="B39" s="1">
         <f>Eor!C36 * 0.5</f>
-        <v>6377.7442662000003</v>
+        <v>3367.1384119871791</v>
       </c>
       <c r="C39" s="1">
         <f>Lanyuak!E36 * 0.5</f>
-        <v>6079.524069000001</v>
+        <v>3212.2338585267253</v>
       </c>
       <c r="D39" s="1">
         <f>Mumberes!E36*0.5</f>
-        <v>1257.4260116353003</v>
+        <v>593.57875124859993</v>
       </c>
       <c r="E39" s="1">
         <f>Kabianga!C36*0.5</f>
-        <v>6622.907614661448</v>
+        <v>2824.1775840482123</v>
       </c>
       <c r="F39" s="1">
         <f>Kipsigis!B36*0.5</f>
-        <v>4335.9476626222977</v>
+        <v>1863.0322481115707</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="0"/>
-        <v>24673.549624119049</v>
+        <v>11860.160853922289</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="1">
+      <c r="A40" s="4">
         <v>2060</v>
       </c>
       <c r="B40" s="1">
         <f>Eor!C37 * 0.5</f>
-        <v>6138.1548416999995</v>
+        <v>3219.7377488822258</v>
       </c>
       <c r="C40" s="1">
         <f>Lanyuak!E37 * 0.5</f>
-        <v>5851.2696818000004</v>
+        <v>3071.6769302007042</v>
       </c>
       <c r="D40" s="1">
         <f>Mumberes!E37*0.5</f>
-        <v>1204.2938293840998</v>
+        <v>560.1259334138</v>
       </c>
       <c r="E40" s="1">
         <f>Kabianga!C37*0.5</f>
-        <v>6252.7974928714002</v>
+        <v>2628.8242776496541</v>
       </c>
       <c r="F40" s="1">
         <f>Kipsigis!B37*0.5</f>
-        <v>4095.0863598393371</v>
+        <v>1734.4971553359032</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="0"/>
-        <v>23541.602205594838</v>
+        <v>11214.862045482287</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="1">
+      <c r="A41" s="4">
         <v>2061</v>
       </c>
       <c r="B41" s="1">
         <f>Eor!C38 * 0.5</f>
-        <v>5907.7772397999997</v>
+        <v>3078.8481329323613</v>
       </c>
       <c r="C41" s="1">
         <f>Lanyuak!E38 * 0.5</f>
-        <v>5631.7875337999994</v>
+        <v>2937.3259805822727</v>
       </c>
       <c r="D41" s="1">
         <f>Mumberes!E38*0.5</f>
-        <v>1153.4886211394</v>
+        <v>528.5783922887</v>
       </c>
       <c r="E41" s="1">
         <f>Kabianga!C38*0.5</f>
-        <v>5903.6230690654102</v>
+        <v>2447.0442255119624</v>
       </c>
       <c r="F41" s="1">
         <f>Kipsigis!B38*0.5</f>
-        <v>3867.7198936383998</v>
+        <v>1614.8504423511949</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="0"/>
-        <v>22464.396357443213</v>
+        <v>10606.647173666492</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="1">
+      <c r="A42" s="4">
         <v>2062</v>
       </c>
       <c r="B42" s="1">
         <f>Eor!C39 * 0.5</f>
-        <v>5686.2411976999992</v>
+        <v>2944.17700910651</v>
       </c>
       <c r="C42" s="1">
         <f>Lanyuak!E39 * 0.5</f>
-        <v>5420.7248254000006</v>
+        <v>2808.90227752176</v>
       </c>
       <c r="D42" s="1">
         <f>Mumberes!E39*0.5</f>
-        <v>1104.9025516802001</v>
+        <v>498.82596037169998</v>
       </c>
       <c r="E42" s="1">
         <f>Kabianga!C39*0.5</f>
-        <v>5574.177035783282</v>
+        <v>2277.8881454892271</v>
       </c>
       <c r="F42" s="1">
         <f>Kipsigis!B39*0.5</f>
-        <v>3653.0798183632642</v>
+        <v>1503.4747431162552</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="0"/>
-        <v>21439.125428926745</v>
+        <v>10033.268135605453</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="1">
+      <c r="A43" s="4">
         <v>2063</v>
       </c>
       <c r="B43" s="1">
         <f>Eor!C40 * 0.5</f>
-        <v>5473.1948780000002</v>
+        <v>2815.44538740798</v>
       </c>
       <c r="C43" s="1">
         <f>Lanyuak!E40 * 0.5</f>
-        <v>5217.7466056000003</v>
+        <v>2686.1400087148313</v>
       </c>
       <c r="D43" s="1">
         <f>Mumberes!E40*0.5</f>
-        <v>1058.4336033843001</v>
+        <v>470.7649035869</v>
       </c>
       <c r="E43" s="1">
         <f>Kabianga!C40*0.5</f>
-        <v>5263.3239406504599</v>
+        <v>2120.4738391053802</v>
       </c>
       <c r="F43" s="1">
         <f>Kipsigis!B40*0.5</f>
-        <v>3450.4427745991438</v>
+        <v>1399.7959361570147</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="0"/>
-        <v>20463.141802233902</v>
+        <v>9492.6200749721065</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="1">
+      <c r="A44" s="4">
         <v>2064</v>
       </c>
       <c r="B44" s="1">
         <f>Eor!C41 * 0.5</f>
-        <v>5268.3013590999999</v>
+        <v>2692.3871780411309</v>
       </c>
       <c r="C44" s="1">
         <f>Lanyuak!E41 * 0.5</f>
-        <v>5022.5278908</v>
+        <v>2568.7856485947782</v>
       </c>
       <c r="D44" s="1">
         <f>Mumberes!E41*0.5</f>
-        <v>1013.9834535909001</v>
+        <v>444.29731855990002</v>
       </c>
       <c r="E44" s="1">
         <f>Kabianga!C41*0.5</f>
-        <v>4969.9956836370629</v>
+        <v>1973.981367497471</v>
       </c>
       <c r="F44" s="1">
         <f>Kipsigis!B41*0.5</f>
-        <v>3259.1277011353677</v>
+        <v>1303.2800662797888</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="0"/>
-        <v>19533.93608826333</v>
+        <v>8982.7315789730692</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="1">
+      <c r="A45" s="4">
         <v>2065</v>
       </c>
       <c r="B45" s="1">
         <f>Eor!C42 * 0.5</f>
-        <v>5071.2324933999998</v>
+        <v>2574.7485623724842</v>
       </c>
       <c r="C45" s="1">
         <f>Lanyuak!E42 * 0.5</f>
-        <v>4834.7638640000005</v>
+        <v>2456.5973593167637</v>
       </c>
       <c r="D45" s="1">
         <f>Mumberes!E42*0.5</f>
-        <v>971.46106474039993</v>
+        <v>419.3311195151</v>
       </c>
       <c r="E45" s="1">
         <f>Kabianga!C42*0.5</f>
-        <v>4693.1873205393395</v>
+        <v>1837.6485851623183</v>
       </c>
       <c r="F45" s="1">
         <f>Kipsigis!B42*0.5</f>
-        <v>3078.4932349394576</v>
+        <v>1213.4304922867395</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="0"/>
-        <v>18649.137977619197</v>
+        <v>8501.7561186534058</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5234,7 +5193,7 @@
       </c>
       <c r="H47" s="1">
         <f>SUM(H6:H45)</f>
-        <v>3543669.9909584285</v>
+        <v>2179674.8622737951</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5243,7 +5202,7 @@
       </c>
       <c r="H48" s="1">
         <f>H47/40</f>
-        <v>88591.749773960706</v>
+        <v>54491.871556844875</v>
       </c>
     </row>
   </sheetData>
@@ -5257,7 +5216,7 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.83203125"/>
     <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10.83203125" style="1"/>
     <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -5265,504 +5224,502 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
       <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5">
-        <v>47.510150000000003</v>
-      </c>
-      <c r="B3" s="5">
-        <v>50.02187</v>
+      <c r="A3">
+        <v>30.00965219319507</v>
+      </c>
+      <c r="B3">
+        <v>32.520492789975343</v>
       </c>
       <c r="C3" s="1">
-        <f>A3*0.4*$G$3 + B3*0.6*$G$3</f>
-        <v>215038.37743400002</v>
-      </c>
-      <c r="G3" s="6">
+        <f t="shared" ref="C3:C42" si="0">A3*0.4*$G$3 + B3*0.6*$G$3</f>
+        <v>138261.37879039178</v>
+      </c>
+      <c r="G3" s="3">
         <v>4387</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5">
-        <v>26.930399999999999</v>
-      </c>
-      <c r="B4" s="5">
-        <v>28.359539999999999</v>
+      <c r="A4">
+        <v>16.987954339783851</v>
+      </c>
+      <c r="B4">
+        <v>18.412798044651471</v>
       </c>
       <c r="C4" s="1">
-        <f>A4*0.4*$G$3 + B4*0.6*$G$3</f>
-        <v>121905.44710799999</v>
+        <f t="shared" si="0"/>
+        <v>78276.6292885843</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5">
-        <v>18.402439999999999</v>
-      </c>
-      <c r="B5" s="5">
-        <v>19.387350000000001</v>
+      <c r="A5">
+        <v>11.57380885566908</v>
+      </c>
+      <c r="B5">
+        <v>12.549911822638251</v>
       </c>
       <c r="C5" s="1">
-        <f>A5*0.4*$G$3 + B5*0.6*$G$3</f>
-        <v>83323.984381999995</v>
+        <f t="shared" si="0"/>
+        <v>53343.597679476501</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5">
-        <v>13.79119</v>
-      </c>
-      <c r="B6" s="5">
-        <v>14.539239999999999</v>
+      <c r="A6">
+        <v>8.632595654473187</v>
+      </c>
+      <c r="B6">
+        <v>9.3670054257693689</v>
       </c>
       <c r="C6" s="1">
-        <f>A6*0.4*$G$3 + B6*0.6*$G$3</f>
-        <v>62470.96774</v>
+        <f t="shared" si="0"/>
+        <v>39804.310536179677</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="5">
-        <v>11.211029999999999</v>
-      </c>
-      <c r="B7" s="5">
-        <v>11.82938</v>
+      <c r="A7">
+        <v>6.9753653233964599</v>
+      </c>
+      <c r="B7">
+        <v>7.5753266113888129</v>
       </c>
       <c r="C7" s="1">
-        <f>A7*0.4*$G$3 + B7*0.6*$G$3</f>
-        <v>50810.409480000002</v>
+        <f t="shared" si="0"/>
+        <v>32180.14577599374</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="5">
-        <v>9.6973249999999993</v>
-      </c>
-      <c r="B8" s="5">
-        <v>10.241949999999999</v>
+      <c r="A8">
+        <v>5.9936492958398118</v>
+      </c>
+      <c r="B8">
+        <v>6.5153692492147384</v>
       </c>
       <c r="C8" s="1">
-        <f>A8*0.4*$G$3 + B8*0.6*$G$3</f>
-        <v>43975.726699999999</v>
+        <f t="shared" si="0"/>
+        <v>27667.410722122735</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="5">
-        <v>8.7495619999999992</v>
-      </c>
-      <c r="B9" s="5">
-        <v>9.2498970000000007</v>
+      <c r="A9">
+        <v>5.3715258575554161</v>
+      </c>
+      <c r="B9">
+        <v>5.8447451583360577</v>
       </c>
       <c r="C9" s="1">
-        <f>A9*0.4*$G$3 + B9*0.6*$G$3</f>
-        <v>39701.310280999998</v>
+        <f t="shared" si="0"/>
+        <v>24810.491780610413</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="5">
-        <v>8.1058140000000005</v>
-      </c>
-      <c r="B10" s="5">
-        <v>8.5774629999999998</v>
+      <c r="A10">
+        <v>4.9435315731825353</v>
+      </c>
+      <c r="B10">
+        <v>5.3841525533161132</v>
       </c>
       <c r="C10" s="1">
-        <f>A10*0.4*$G$3 + B10*0.6*$G$3</f>
-        <v>36801.680515799999</v>
+        <f t="shared" si="0"/>
+        <v>22847.075555459385</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5">
-        <v>7.6282769999999998</v>
-      </c>
-      <c r="B11" s="5">
-        <v>8.0795779999999997</v>
+      <c r="A11">
+        <v>4.6225078275165901</v>
+      </c>
+      <c r="B11">
+        <v>5.0391601637318741</v>
       </c>
       <c r="C11" s="1">
-        <f>A11*0.4*$G$3 + B11*0.6*$G$3</f>
-        <v>34653.165691199996</v>
+        <f t="shared" si="0"/>
+        <v>21375.654118701153</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="5">
-        <v>7.2441420000000001</v>
-      </c>
-      <c r="B12" s="5">
-        <v>7.6796139999999999</v>
+      <c r="A12">
+        <v>4.3623283808112392</v>
+      </c>
+      <c r="B12">
+        <v>4.7598055311291132</v>
       </c>
       <c r="C12" s="1">
-        <f>A12*0.4*$G$3 + B12*0.6*$G$3</f>
-        <v>32926.300352399994</v>
+        <f t="shared" si="0"/>
+        <v>20183.773961685616</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="5">
-        <v>6.914771</v>
-      </c>
-      <c r="B13" s="5">
-        <v>7.3369179999999998</v>
+      <c r="A13">
+        <v>4.1384543635296511</v>
+      </c>
+      <c r="B13">
+        <v>4.5195190769488249</v>
       </c>
       <c r="C13" s="1">
-        <f>A13*0.4*$G$3 + B13*0.6*$G$3</f>
-        <v>31446.275710399997</v>
+        <f t="shared" si="0"/>
+        <v>19158.43783146653</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="5">
-        <v>6.6195370000000002</v>
-      </c>
-      <c r="B14" s="5">
-        <v>7.0297980000000004</v>
+      <c r="A14">
+        <v>3.937732847632494</v>
+      </c>
+      <c r="B14">
+        <v>4.3040679745768431</v>
       </c>
       <c r="C14" s="1">
-        <f>A14*0.4*$G$3 + B14*0.6*$G$3</f>
-        <v>30119.797823200002</v>
+        <f t="shared" si="0"/>
+        <v>18239.101323706665</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="5">
-        <v>6.3473170000000003</v>
-      </c>
-      <c r="B15" s="5">
-        <v>6.7465700000000002</v>
+      <c r="A15">
+        <v>3.7530278707419309</v>
+      </c>
+      <c r="B15">
+        <v>4.1057378646719469</v>
       </c>
       <c r="C15" s="1">
-        <f>A15*0.4*$G$3 + B15*0.6*$G$3</f>
-        <v>28896.5934256</v>
+        <f t="shared" si="0"/>
+        <v>17392.936514967441</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="5">
-        <v>6.0920189999999996</v>
-      </c>
-      <c r="B16" s="5">
-        <v>6.4808380000000003</v>
+      <c r="A16">
+        <v>3.580389571916371</v>
+      </c>
+      <c r="B16">
+        <v>3.9202653685046021</v>
       </c>
       <c r="C16" s="1">
-        <f>A16*0.4*$G$3 + B16*0.6*$G$3</f>
-        <v>27749.136724800002</v>
+        <f t="shared" si="0"/>
+        <v>16601.790123776664</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="5">
-        <v>5.8502130000000001</v>
-      </c>
-      <c r="B17" s="5">
-        <v>6.229012</v>
+      <c r="A17">
+        <v>3.417559876049566</v>
+      </c>
+      <c r="B17">
+        <v>3.7452190228488238</v>
       </c>
       <c r="C17" s="1">
-        <f>A17*0.4*$G$3 + B17*0.6*$G$3</f>
-        <v>26661.959158800004</v>
+        <f t="shared" si="0"/>
+        <v>15855.299582434453</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5">
-        <v>5.6198889999999997</v>
-      </c>
-      <c r="B18" s="5">
-        <v>5.9889950000000001</v>
+      <c r="A18">
+        <v>3.263183030652741</v>
+      </c>
+      <c r="B18">
+        <v>3.579143998906166</v>
       </c>
       <c r="C18" s="1">
-        <f>A18*0.4*$G$3 + B18*0.6*$G$3</f>
-        <v>25626.013856199999</v>
+        <f t="shared" si="0"/>
+        <v>15147.256416110238</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="5">
-        <v>5.3997950000000001</v>
-      </c>
-      <c r="B19" s="5">
-        <v>5.7594830000000004</v>
+      <c r="A19">
+        <v>3.1163881772276998</v>
+      </c>
+      <c r="B19">
+        <v>3.4211099262216802</v>
       </c>
       <c r="C19" s="1">
-        <f>A19*0.4*$G$3 + B19*0.6*$G$3</f>
-        <v>24635.671418600003</v>
+        <f t="shared" si="0"/>
+        <v>14473.683521199873</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="5">
-        <v>5.1890859999999996</v>
-      </c>
-      <c r="B20" s="5">
-        <v>5.5396049999999999</v>
+      <c r="A20">
+        <v>2.9765683948116548</v>
+      </c>
+      <c r="B20">
+        <v>3.2704715788027752</v>
       </c>
       <c r="C20" s="1">
-        <f>A20*0.4*$G$3 + B20*0.6*$G$3</f>
-        <v>23687.1563938</v>
+        <f t="shared" si="0"/>
+        <v>13831.817508940157</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="5">
-        <v>4.9871449999999999</v>
-      </c>
-      <c r="B21" s="5">
-        <v>5.3287259999999996</v>
+      <c r="A21">
+        <v>2.8432635417130001</v>
+      </c>
+      <c r="B21">
+        <v>3.1267420086958659</v>
       </c>
       <c r="C21" s="1">
-        <f>A21*0.4*$G$3 + B21*0.6*$G$3</f>
-        <v>22777.714623199998</v>
+        <f t="shared" si="0"/>
+        <v>13219.569178287231</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="5">
-        <v>4.7934809999999999</v>
-      </c>
-      <c r="B22" s="5">
-        <v>5.1263420000000002</v>
+      <c r="A22">
+        <v>2.7160979555368581</v>
+      </c>
+      <c r="B22">
+        <v>2.9895251037374679</v>
       </c>
       <c r="C22" s="1">
-        <f>A22*0.4*$G$3 + B22*0.6*$G$3</f>
-        <v>21905.157871199997</v>
+        <f t="shared" si="0"/>
+        <v>12635.236670433842</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="5">
-        <v>4.6076800000000002</v>
-      </c>
-      <c r="B23" s="5">
-        <v>4.9320310000000003</v>
+      <c r="A23">
+        <v>2.59474716010061</v>
+      </c>
+      <c r="B23">
+        <v>2.8584795633981912</v>
       </c>
       <c r="C23" s="1">
-        <f>A23*0.4*$G$3 + B23*0.6*$G$3</f>
-        <v>21067.648862200003</v>
+        <f t="shared" si="0"/>
+        <v>12077.352223321268</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="5">
-        <v>4.429373</v>
-      </c>
-      <c r="B24" s="5">
-        <v>4.7454169999999998</v>
+      <c r="A24">
+        <v>2.4789199211009771</v>
+      </c>
+      <c r="B24">
+        <v>2.73329949737338</v>
       </c>
       <c r="C24" s="1">
-        <f>A24*0.4*$G$3 + B24*0.6*$G$3</f>
-        <v>20263.550367799999</v>
+        <f t="shared" si="0"/>
+        <v>11544.599614534207</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="5">
-        <v>4.258222</v>
-      </c>
-      <c r="B25" s="5">
-        <v>4.5661569999999996</v>
+      <c r="A25">
+        <v>2.3683484330857141</v>
+      </c>
+      <c r="B25">
+        <v>2.6137038291373118</v>
       </c>
       <c r="C25" s="1">
-        <f>A25*0.4*$G$3 + B25*0.6*$G$3</f>
-        <v>19491.366420999999</v>
+        <f t="shared" si="0"/>
+        <v>11035.769049434042</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5">
-        <v>4.0939160000000001</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4.3939339999999998</v>
+      <c r="A26">
+        <v>2.2627828228948439</v>
+      </c>
+      <c r="B26">
+        <v>2.4994303726551741</v>
       </c>
       <c r="C26" s="1">
-        <f>A26*0.4*$G$3 + B26*0.6*$G$3</f>
-        <v>18749.716871599998</v>
+        <f t="shared" si="0"/>
+        <v>10549.731924518821</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="5">
-        <v>3.936159</v>
-      </c>
-      <c r="B27" s="5">
-        <v>4.2284470000000001</v>
+      <c r="A27">
+        <v>2.16198795251537</v>
+      </c>
+      <c r="B27">
+        <v>2.3902323977628162</v>
       </c>
       <c r="C27" s="1">
-        <f>A27*0.4*$G$3 + B27*0.6*$G$3</f>
-        <v>18037.2900066</v>
+        <f t="shared" si="0"/>
+        <v>10085.426176465255</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="5">
-        <v>3.7846739999999999</v>
-      </c>
-      <c r="B28" s="5">
-        <v>4.0694160000000004</v>
+      <c r="A28">
+        <v>2.065741454276818</v>
+      </c>
+      <c r="B28">
+        <v>2.2858765286843168</v>
       </c>
       <c r="C28" s="1">
-        <f>A28*0.4*$G$3 + B28*0.6*$G$3</f>
-        <v>17352.8627304</v>
+        <f t="shared" si="0"/>
+        <v>9641.8473027678192</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="5">
-        <v>3.639195</v>
-      </c>
-      <c r="B29" s="5">
-        <v>3.916569</v>
+      <c r="A29">
+        <v>1.9738324333458011</v>
+      </c>
+      <c r="B29">
+        <v>2.1861413638588609</v>
       </c>
       <c r="C29" s="1">
-        <f>A29*0.4*$G$3 + B29*0.6*$G$3</f>
-        <v>16695.252307800001</v>
+        <f t="shared" si="0"/>
+        <v>9218.0424519845055</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="5">
-        <v>3.4994710000000002</v>
-      </c>
-      <c r="B30" s="5">
-        <v>3.7696519999999998</v>
+      <c r="A30">
+        <v>1.886060537877251</v>
+      </c>
+      <c r="B30">
+        <v>2.0908164926691861</v>
       </c>
       <c r="C30" s="1">
-        <f>A30*0.4*$G$3 + B30*0.6*$G$3</f>
-        <v>16063.349705199998</v>
+        <f t="shared" si="0"/>
+        <v>8813.1062038708315</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="5">
-        <v>3.365262</v>
-      </c>
-      <c r="B31" s="5">
-        <v>3.6284209999999999</v>
+      <c r="A31">
+        <v>1.802235237463397</v>
+      </c>
+      <c r="B31">
+        <v>1.999701736576337</v>
       </c>
       <c r="C31" s="1">
-        <f>A31*0.4*$G$3 + B31*0.6*$G$3</f>
-        <v>15456.091513799998</v>
+        <f t="shared" si="0"/>
+        <v>8426.177305717003</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="5">
-        <v>3.2363390000000001</v>
-      </c>
-      <c r="B32" s="5">
-        <v>3.492642</v>
+      <c r="A32">
+        <v>1.7221752247669</v>
+      </c>
+      <c r="B32">
+        <v>1.9126065225557529</v>
       </c>
       <c r="C32" s="1">
-        <f>A32*0.4*$G$3 + B32*0.6*$G$3</f>
-        <v>14872.459949599999</v>
+        <f t="shared" si="0"/>
+        <v>8056.4359730922079</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="5">
-        <v>3.1124830000000001</v>
-      </c>
-      <c r="B33" s="5">
-        <v>3.3620939999999999</v>
+      <c r="A33">
+        <v>1.6457078944949519</v>
+      </c>
+      <c r="B33">
+        <v>1.8293493392475899</v>
       </c>
       <c r="C33" s="1">
-        <f>A33*0.4*$G$3 + B33*0.6*$G$3</f>
-        <v>14311.488995200001</v>
+        <f t="shared" si="0"/>
+        <v>7703.1015440272477</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="5">
-        <v>2.9934859999999999</v>
-      </c>
-      <c r="B34" s="5">
-        <v>3.236564</v>
+      <c r="A34">
+        <v>1.5726688747120221</v>
+      </c>
+      <c r="B34">
+        <v>1.7497572488004021</v>
       </c>
       <c r="C34" s="1">
-        <f>A34*0.4*$G$3 + B34*0.6*$G$3</f>
-        <v>13772.252993599999</v>
+        <f t="shared" si="0"/>
+        <v>7365.4303716370741</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="5">
-        <v>2.879149</v>
-      </c>
-      <c r="B35" s="5">
-        <v>3.11585</v>
+      <c r="A35">
+        <v>1.5029015965484549</v>
+      </c>
+      <c r="B35">
+        <v>1.6736654393530299</v>
       </c>
       <c r="C35" s="1">
-        <f>A35*0.4*$G$3 + B35*0.6*$G$3</f>
-        <v>13253.871035200002</v>
+        <f t="shared" si="0"/>
+        <v>7042.713891088275</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="5">
-        <v>2.769279</v>
-      </c>
-      <c r="B36" s="5">
-        <v>2.9997560000000001</v>
+      <c r="A36">
+        <v>1.436256894256758</v>
+      </c>
+      <c r="B36">
+        <v>1.6009168094873489</v>
       </c>
       <c r="C36" s="1">
-        <f>A36*0.4*$G$3 + B36*0.6*$G$3</f>
-        <v>12755.488532400001</v>
+        <f t="shared" si="0"/>
+        <v>6734.2768239743582</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="5">
-        <v>2.663697</v>
-      </c>
-      <c r="B37" s="5">
-        <v>2.888099</v>
+      <c r="A37">
+        <v>1.3725926307444121</v>
+      </c>
+      <c r="B37">
+        <v>1.5313615794142379</v>
       </c>
       <c r="C37" s="1">
-        <f>A37*0.4*$G$3 + B37*0.6*$G$3</f>
-        <v>12276.309683399999</v>
+        <f t="shared" si="0"/>
+        <v>6439.4754977644516</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="5">
-        <v>2.562227</v>
-      </c>
-      <c r="B38" s="5">
-        <v>2.7806999999999999</v>
+      <c r="A38">
+        <v>1.3117733454202301</v>
+      </c>
+      <c r="B38">
+        <v>1.4648569255076751</v>
       </c>
       <c r="C38" s="1">
-        <f>A38*0.4*$G$3 + B38*0.6*$G$3</f>
-        <v>11815.554479599999</v>
+        <f t="shared" si="0"/>
+        <v>6157.6962658647226</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="5">
-        <v>2.4647019999999999</v>
-      </c>
-      <c r="B39" s="5">
-        <v>2.6773889999999998</v>
+      <c r="A39">
+        <v>1.253669922144492</v>
+      </c>
+      <c r="B39">
+        <v>1.401266635830813</v>
       </c>
       <c r="C39" s="1">
-        <f>A39*0.4*$G$3 + B39*0.6*$G$3</f>
-        <v>11372.482395399998</v>
+        <f t="shared" si="0"/>
+        <v>5888.35401821302</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="5">
-        <v>2.3709639999999998</v>
-      </c>
-      <c r="B40" s="5">
-        <v>2.578004</v>
+      <c r="A40">
+        <v>1.1981592756147521</v>
+      </c>
+      <c r="B40">
+        <v>1.3404607848823009</v>
       </c>
       <c r="C40" s="1">
-        <f>A40*0.4*$G$3 + B40*0.6*$G$3</f>
-        <v>10946.389756</v>
+        <f t="shared" si="0"/>
+        <v>5630.89077481596</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="5">
-        <v>2.2808600000000001</v>
-      </c>
-      <c r="B41" s="5">
-        <v>2.4823909999999998</v>
+      <c r="A41">
+        <v>1.1451240548341941</v>
+      </c>
+      <c r="B41">
+        <v>1.2823154261299361</v>
       </c>
       <c r="C41" s="1">
-        <f>A41*0.4*$G$3 + B41*0.6*$G$3</f>
-        <v>10536.6027182</v>
+        <f t="shared" si="0"/>
+        <v>5384.7743560822619</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="5">
-        <v>2.1942439999999999</v>
-      </c>
-      <c r="B42" s="5">
-        <v>2.3903979999999998</v>
+      <c r="A42">
+        <v>1.0944523625117359</v>
+      </c>
+      <c r="B42">
+        <v>1.2267123011204979</v>
       </c>
       <c r="C42" s="1">
-        <f>A42*0.4*$G$3 + B42*0.6*$G$3</f>
-        <v>10142.4649868</v>
+        <f t="shared" si="0"/>
+        <v>5149.4971247449685</v>
       </c>
     </row>
   </sheetData>
@@ -5775,7 +5732,7 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="8.83203125"/>
     <col min="5" max="5" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="1"/>
     <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -5783,752 +5740,748 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
       <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5">
-        <v>49.955860000000001</v>
-      </c>
-      <c r="B3" s="5">
-        <v>50.042589999999997</v>
-      </c>
-      <c r="C3" s="5">
-        <v>50.042589999999997</v>
-      </c>
-      <c r="D3" s="5">
-        <v>47.949440000000003</v>
+      <c r="A3">
+        <v>32.454500939573443</v>
+      </c>
+      <c r="B3">
+        <v>32.541203692547008</v>
+      </c>
+      <c r="C3">
+        <v>32.541203692547008</v>
+      </c>
+      <c r="D3">
+        <v>30.448783101555762</v>
       </c>
       <c r="E3" s="1">
         <f>A3*0.2*$G$3 + B3*0.15*$G$3 + C3*0.15*$G$3 + D3*0.4*$G$3</f>
-        <v>204835.74910000002</v>
+        <v>131814.34275029189</v>
       </c>
       <c r="G3" s="1">
         <v>4636</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5">
-        <v>28.32197</v>
-      </c>
-      <c r="B4" s="5">
-        <v>28.37133</v>
-      </c>
-      <c r="C4" s="5">
-        <v>28.37133</v>
-      </c>
-      <c r="D4" s="5">
-        <v>27.180309999999999</v>
+      <c r="A4">
+        <v>18.375342256074731</v>
+      </c>
+      <c r="B4">
+        <v>18.424553258170381</v>
+      </c>
+      <c r="C4">
+        <v>18.424553258170381</v>
+      </c>
+      <c r="D4">
+        <v>17.237111769010198</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E42" si="0">A4*0.2*$G$3 + B4*0.15*$G$3 + C4*0.15*$G$3 + D4*0.4*$G$3</f>
-        <v>116122.143212</v>
+        <v>74626.986075748369</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5">
-        <v>19.361450000000001</v>
-      </c>
-      <c r="B5" s="5">
-        <v>19.395479999999999</v>
-      </c>
-      <c r="C5" s="5">
-        <v>19.395479999999999</v>
-      </c>
-      <c r="D5" s="5">
-        <v>18.5746</v>
+      <c r="A5">
+        <v>12.524241687218289</v>
+      </c>
+      <c r="B5">
+        <v>12.557968317817579</v>
+      </c>
+      <c r="C5">
+        <v>12.557968317817579</v>
+      </c>
+      <c r="D5">
+        <v>11.744436352874651</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>79371.908263999998</v>
+        <v>50856.98200158024</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5">
-        <v>14.519550000000001</v>
-      </c>
-      <c r="B6" s="5">
-        <v>14.54541</v>
-      </c>
-      <c r="C6" s="5">
-        <v>14.54541</v>
-      </c>
-      <c r="D6" s="5">
-        <v>13.92187</v>
+      <c r="A6">
+        <v>9.3476787922117719</v>
+      </c>
+      <c r="B6">
+        <v>9.3730711732124945</v>
+      </c>
+      <c r="C6">
+        <v>9.3730711732124945</v>
+      </c>
+      <c r="D6">
+        <v>8.7609025439806487</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>59508.998716000002</v>
+        <v>37949.452841400409</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="5">
-        <v>11.813090000000001</v>
-      </c>
-      <c r="B7" s="5">
-        <v>11.834490000000001</v>
-      </c>
-      <c r="C7" s="5">
-        <v>11.834490000000001</v>
-      </c>
-      <c r="D7" s="5">
-        <v>11.31898</v>
+      <c r="A7">
+        <v>7.559525069141027</v>
+      </c>
+      <c r="B7">
+        <v>7.5802861389118732</v>
+      </c>
+      <c r="C7">
+        <v>7.5802861389118732</v>
+      </c>
+      <c r="D7">
+        <v>7.0801096562298271</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>48402.422252000004</v>
+        <v>30681.208952618785</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="5">
-        <v>10.227589999999999</v>
-      </c>
-      <c r="B8" s="5">
-        <v>10.246449999999999</v>
-      </c>
-      <c r="C8" s="5">
-        <v>10.246449999999999</v>
-      </c>
-      <c r="D8" s="5">
-        <v>9.7923369999999998</v>
+      <c r="A8">
+        <v>6.5016160582364222</v>
+      </c>
+      <c r="B8">
+        <v>6.5196860114279502</v>
+      </c>
+      <c r="C8">
+        <v>6.5196860114279502</v>
+      </c>
+      <c r="D8">
+        <v>6.0846644343469478</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>41892.693840799999</v>
+        <v>26379.279440943785</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="5">
-        <v>9.2366960000000002</v>
-      </c>
-      <c r="B9" s="5">
-        <v>9.2540399999999998</v>
-      </c>
-      <c r="C9" s="5">
-        <v>9.2540399999999998</v>
-      </c>
-      <c r="D9" s="5">
-        <v>8.8367819999999995</v>
+      <c r="A9">
+        <v>5.8322592677101186</v>
+      </c>
+      <c r="B9">
+        <v>5.8486642736966603</v>
+      </c>
+      <c r="C9">
+        <v>5.8486642736966603</v>
+      </c>
+      <c r="D9">
+        <v>5.4540167694590496</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>37821.711903999996</v>
+        <v>23655.921762163001</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="5">
-        <v>8.5650089999999999</v>
-      </c>
-      <c r="B10" s="5">
-        <v>8.5813729999999993</v>
-      </c>
-      <c r="C10" s="5">
-        <v>8.5813729999999993</v>
-      </c>
-      <c r="D10" s="5">
-        <v>8.1879740000000005</v>
+      <c r="A10">
+        <v>5.3725166207071027</v>
+      </c>
+      <c r="B10">
+        <v>5.3878049938780164</v>
+      </c>
+      <c r="C10">
+        <v>5.3878049938780164</v>
+      </c>
+      <c r="D10">
+        <v>5.0202829698626914</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>35060.2288988</v>
+        <v>21784.369335518546</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5">
-        <v>8.0676509999999997</v>
-      </c>
-      <c r="B11" s="5">
-        <v>8.0833220000000008</v>
-      </c>
-      <c r="C11" s="5">
-        <v>8.0833220000000008</v>
-      </c>
-      <c r="D11" s="5">
-        <v>7.7068380000000003</v>
+      <c r="A11">
+        <v>5.0281479619988314</v>
+      </c>
+      <c r="B11">
+        <v>5.0426169222301516</v>
+      </c>
+      <c r="C11">
+        <v>5.0426169222301516</v>
+      </c>
+      <c r="D11">
+        <v>4.6950323027858936</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>33014.170632000001</v>
+        <v>20381.838308089173</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="5">
-        <v>7.6680960000000002</v>
-      </c>
-      <c r="B12" s="5">
-        <v>7.6832289999999999</v>
-      </c>
-      <c r="C12" s="5">
-        <v>7.6832289999999999</v>
-      </c>
-      <c r="D12" s="5">
-        <v>7.3198970000000001</v>
+      <c r="A12">
+        <v>4.7492916217833283</v>
+      </c>
+      <c r="B12">
+        <v>4.7631059691703159</v>
+      </c>
+      <c r="C12">
+        <v>4.7631059691703159</v>
+      </c>
+      <c r="D12">
+        <v>4.4314673811605827</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="0"/>
-        <v>31369.710501200003</v>
+        <v>19245.78408526376</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="5">
-        <v>7.3257440000000003</v>
-      </c>
-      <c r="B13" s="5">
-        <v>7.3404259999999999</v>
-      </c>
-      <c r="C13" s="5">
-        <v>7.3404259999999999</v>
-      </c>
-      <c r="D13" s="5">
-        <v>6.9881609999999998</v>
+      <c r="A13">
+        <v>4.5094313569362283</v>
+      </c>
+      <c r="B13">
+        <v>4.5226858177392204</v>
+      </c>
+      <c r="C13">
+        <v>4.5226858177392204</v>
+      </c>
+      <c r="D13">
+        <v>4.2046939643944086</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>29960.340076</v>
+        <v>18268.480677035972</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="5">
-        <v>7.0189310000000003</v>
-      </c>
-      <c r="B14" s="5">
-        <v>7.0332100000000004</v>
-      </c>
-      <c r="C14" s="5">
-        <v>7.0332100000000004</v>
-      </c>
-      <c r="D14" s="5">
-        <v>6.6908159999999999</v>
+      <c r="A14">
+        <v>4.2943626893457889</v>
+      </c>
+      <c r="B14">
+        <v>4.3071147447958351</v>
+      </c>
+      <c r="C14">
+        <v>4.3071147447958351</v>
+      </c>
+      <c r="D14">
+        <v>4.0013700615293466</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>28697.190481600002</v>
+        <v>17392.208914723484</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="5">
-        <v>6.7359859999999996</v>
-      </c>
-      <c r="B15" s="5">
-        <v>6.749892</v>
-      </c>
-      <c r="C15" s="5">
-        <v>6.749892</v>
-      </c>
-      <c r="D15" s="5">
-        <v>6.4166400000000001</v>
+      <c r="A15">
+        <v>4.0963864305964011</v>
+      </c>
+      <c r="B15">
+        <v>4.108673630090057</v>
+      </c>
+      <c r="C15">
+        <v>4.108673630090057</v>
+      </c>
+      <c r="D15">
+        <v>3.814258375512475</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>27532.373228800003</v>
+        <v>16585.673514728569</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="5">
-        <v>6.4705240000000002</v>
-      </c>
-      <c r="B16" s="5">
-        <v>6.484076</v>
-      </c>
-      <c r="C16" s="5">
-        <v>6.484076</v>
-      </c>
-      <c r="D16" s="5">
-        <v>6.1594889999999998</v>
+      <c r="A16">
+        <v>3.9112474139993152</v>
+      </c>
+      <c r="B16">
+        <v>3.9230965179304889</v>
+      </c>
+      <c r="C16">
+        <v>3.9230965179304889</v>
+      </c>
+      <c r="D16">
+        <v>3.6393540528445998</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>26439.679155200003</v>
+        <v>15831.569394992915</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5">
-        <v>6.2189569999999996</v>
-      </c>
-      <c r="B17" s="5">
-        <v>6.2321689999999998</v>
-      </c>
-      <c r="C17" s="5">
-        <v>6.2321689999999998</v>
-      </c>
-      <c r="D17" s="5">
-        <v>5.9159040000000003</v>
+      <c r="A17">
+        <v>3.7365187077333442</v>
+      </c>
+      <c r="B17">
+        <v>3.7479505232364918</v>
+      </c>
+      <c r="C17">
+        <v>3.7479505232364918</v>
+      </c>
+      <c r="D17">
+        <v>3.4743685471407888</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>25404.369953200003</v>
+        <v>15120.018767345548</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5">
-        <v>5.97919</v>
-      </c>
-      <c r="B18" s="5">
-        <v>5.9920730000000004</v>
-      </c>
-      <c r="C18" s="5">
-        <v>5.9920730000000004</v>
-      </c>
-      <c r="D18" s="5">
-        <v>5.6838610000000003</v>
+      <c r="A18">
+        <v>3.570748063206679</v>
+      </c>
+      <c r="B18">
+        <v>3.581780007696779</v>
+      </c>
+      <c r="C18">
+        <v>3.581780007696779</v>
+      </c>
+      <c r="D18">
+        <v>3.317928642280938</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
-        <v>24417.8319348</v>
+        <v>14445.104113155685</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5">
-        <v>5.7499209999999996</v>
-      </c>
-      <c r="B19" s="5">
-        <v>5.7624849999999999</v>
-      </c>
-      <c r="C19" s="5">
-        <v>5.7624849999999999</v>
-      </c>
-      <c r="D19" s="5">
-        <v>5.4620959999999998</v>
+      <c r="A19">
+        <v>3.4130066519001518</v>
+      </c>
+      <c r="B19">
+        <v>3.423654117178534</v>
+      </c>
+      <c r="C19">
+        <v>3.423654117178534</v>
+      </c>
+      <c r="D19">
+        <v>3.169152944793078</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
-        <v>23474.701711599999</v>
+        <v>13803.03513463801</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5">
-        <v>5.5302809999999996</v>
-      </c>
-      <c r="B20" s="5">
-        <v>5.5425329999999997</v>
-      </c>
-      <c r="C20" s="5">
-        <v>5.5425329999999997</v>
-      </c>
-      <c r="D20" s="5">
-        <v>5.2497629999999997</v>
+      <c r="A20">
+        <v>3.2626502337344139</v>
+      </c>
+      <c r="B20">
+        <v>3.2729273164980932</v>
+      </c>
+      <c r="C20">
+        <v>3.2729273164980932</v>
+      </c>
+      <c r="D20">
+        <v>3.027427715453745</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
-        <v>22571.391946799999</v>
+        <v>13191.178564041522</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5">
-        <v>5.3196329999999996</v>
-      </c>
-      <c r="B21" s="5">
-        <v>5.3315809999999999</v>
-      </c>
-      <c r="C21" s="5">
-        <v>5.3315809999999999</v>
-      </c>
-      <c r="D21" s="5">
-        <v>5.0462389999999999</v>
+      <c r="A21">
+        <v>3.1191925456364609</v>
+      </c>
+      <c r="B21">
+        <v>3.1291124429751851</v>
+      </c>
+      <c r="C21">
+        <v>3.1291124429751851</v>
+      </c>
+      <c r="D21">
+        <v>2.892288012176901</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
-        <v>21705.272173999998</v>
+        <v>12607.543803784858</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5">
-        <v>5.1174749999999998</v>
-      </c>
-      <c r="B22" s="5">
-        <v>5.1291260000000003</v>
-      </c>
-      <c r="C22" s="5">
-        <v>5.1291260000000003</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4.8510330000000002</v>
+      <c r="A22">
+        <v>2.982237994322654</v>
+      </c>
+      <c r="B22">
+        <v>2.9918132218041129</v>
+      </c>
+      <c r="C22">
+        <v>2.9918132218041129</v>
+      </c>
+      <c r="D22">
+        <v>2.7633544900034841</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
-        <v>20874.266855999998</v>
+        <v>12050.509463483586</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5">
-        <v>4.9233849999999997</v>
-      </c>
-      <c r="B23" s="5">
-        <v>4.9347459999999996</v>
-      </c>
-      <c r="C23" s="5">
-        <v>4.9347459999999996</v>
-      </c>
-      <c r="D23" s="5">
-        <v>4.6637269999999997</v>
+      <c r="A23">
+        <v>2.8514457038355419</v>
+      </c>
+      <c r="B23">
+        <v>2.8606882194018319</v>
+      </c>
+      <c r="C23">
+        <v>2.8606882194018319</v>
+      </c>
+      <c r="D23">
+        <v>2.6402996298637671</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
-        <v>20076.622657599997</v>
+        <v>11518.677265759752</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5">
-        <v>4.7369859999999999</v>
-      </c>
-      <c r="B24" s="5">
-        <v>4.7480640000000003</v>
-      </c>
-      <c r="C24" s="5">
-        <v>4.7480640000000003</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4.4839520000000004</v>
+      <c r="A24">
+        <v>2.7265101523598498</v>
+      </c>
+      <c r="B24">
+        <v>2.7354314299998208</v>
+      </c>
+      <c r="C24">
+        <v>2.7354314299998208</v>
+      </c>
+      <c r="D24">
+        <v>2.5228295390156981</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
-        <v>19310.781419200001</v>
+        <v>11010.793343262514</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5">
-        <v>4.5579369999999999</v>
-      </c>
-      <c r="B25" s="5">
-        <v>4.5687379999999997</v>
-      </c>
-      <c r="C25" s="5">
-        <v>4.5687379999999997</v>
-      </c>
-      <c r="D25" s="5">
-        <v>4.3113700000000001</v>
+      <c r="A25">
+        <v>2.6071505963122039</v>
+      </c>
+      <c r="B25">
+        <v>2.6157616727567712</v>
+      </c>
+      <c r="C25">
+        <v>2.6157616727567712</v>
+      </c>
+      <c r="D25">
+        <v>2.4106740006795402</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
-        <v>18575.324524800002</v>
+        <v>10525.705234230933</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5">
-        <v>4.3859199999999996</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4.3964499999999997</v>
-      </c>
-      <c r="C26" s="5">
-        <v>4.3964499999999997</v>
-      </c>
-      <c r="D26" s="5">
-        <v>4.1456670000000004</v>
+      <c r="A26">
+        <v>2.49310515821989</v>
+      </c>
+      <c r="B26">
+        <v>2.5014166649630738</v>
+      </c>
+      <c r="C26">
+        <v>2.5014166649630738</v>
+      </c>
+      <c r="D26">
+        <v>2.3035809025753671</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
-        <v>17868.932568800003</v>
+        <v>10062.337826067887</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5">
-        <v>4.2206349999999997</v>
-      </c>
-      <c r="B27" s="5">
-        <v>4.2309010000000002</v>
-      </c>
-      <c r="C27" s="5">
-        <v>4.2309010000000002</v>
-      </c>
-      <c r="D27" s="5">
-        <v>3.986548</v>
+      <c r="A27">
+        <v>2.3841273983015872</v>
+      </c>
+      <c r="B27">
+        <v>2.3921495854789279</v>
+      </c>
+      <c r="C27">
+        <v>2.3921495854789279</v>
+      </c>
+      <c r="D27">
+        <v>2.201312998001427</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
-        <v>17190.364494000001</v>
+        <v>9619.6793906831699</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5">
-        <v>4.0617989999999997</v>
-      </c>
-      <c r="B28" s="5">
-        <v>4.0718069999999997</v>
-      </c>
-      <c r="C28" s="5">
-        <v>4.0718069999999997</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3.8337330000000001</v>
+      <c r="A28">
+        <v>2.279984216537656</v>
+      </c>
+      <c r="B28">
+        <v>2.287726972134223</v>
+      </c>
+      <c r="C28">
+        <v>2.287726972134223</v>
+      </c>
+      <c r="D28">
+        <v>2.1036459169079791</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
-        <v>16538.443683599999</v>
+        <v>9196.7730267321494</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5">
-        <v>3.9091450000000001</v>
-      </c>
-      <c r="B29" s="5">
-        <v>3.918901</v>
-      </c>
-      <c r="C29" s="5">
-        <v>3.918901</v>
-      </c>
-      <c r="D29" s="5">
-        <v>3.686957</v>
+      <c r="A29">
+        <v>2.1804544746360408</v>
+      </c>
+      <c r="B29">
+        <v>2.1879273408854281</v>
+      </c>
+      <c r="C29">
+        <v>2.1879273408854281</v>
+      </c>
+      <c r="D29">
+        <v>2.0103668537316541</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="0"/>
-        <v>15912.0598156</v>
+        <v>8792.7110281459718</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5">
-        <v>3.762416</v>
-      </c>
-      <c r="B30" s="5">
-        <v>3.771925</v>
-      </c>
-      <c r="C30" s="5">
-        <v>3.771925</v>
-      </c>
-      <c r="D30" s="5">
-        <v>3.5459679999999998</v>
+      <c r="A30">
+        <v>2.0853280141316901</v>
+      </c>
+      <c r="B30">
+        <v>2.0925402021146859</v>
+      </c>
+      <c r="C30">
+        <v>2.0925402021146859</v>
+      </c>
+      <c r="D30">
+        <v>1.9212736280152141</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
-        <v>15310.148464399999</v>
+        <v>8406.630863595421</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5">
-        <v>3.6213679999999999</v>
-      </c>
-      <c r="B31" s="5">
-        <v>3.630636</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.630636</v>
-      </c>
-      <c r="D31" s="5">
-        <v>3.4105240000000001</v>
+      <c r="A31">
+        <v>1.9944048984711551</v>
+      </c>
+      <c r="B31">
+        <v>2.001365301466151</v>
+      </c>
+      <c r="C31">
+        <v>2.001365301466151</v>
+      </c>
+      <c r="D31">
+        <v>1.836173956153919</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="0"/>
-        <v>14731.696664000003</v>
+        <v>8037.7120674334055</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5">
-        <v>3.4857680000000002</v>
-      </c>
-      <c r="B32" s="5">
-        <v>3.4948009999999998</v>
-      </c>
-      <c r="C32" s="5">
-        <v>3.4948009999999998</v>
-      </c>
-      <c r="D32" s="5">
-        <v>3.2803969999999998</v>
+      <c r="A32">
+        <v>1.907494787160668</v>
+      </c>
+      <c r="B32">
+        <v>1.9142119930592729</v>
+      </c>
+      <c r="C32">
+        <v>1.9142119930592729</v>
+      </c>
+      <c r="D32">
+        <v>1.754884847927751</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
-        <v>14175.7415172</v>
+        <v>7685.1736685994292</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5">
-        <v>3.3553950000000001</v>
-      </c>
-      <c r="B33" s="5">
-        <v>3.364198</v>
-      </c>
-      <c r="C33" s="5">
-        <v>3.364198</v>
-      </c>
-      <c r="D33" s="5">
-        <v>3.1553659999999999</v>
+      <c r="A33">
+        <v>1.824416392490249</v>
+      </c>
+      <c r="B33">
+        <v>1.8308986954592921</v>
+      </c>
+      <c r="C33">
+        <v>1.8308986954592921</v>
+      </c>
+      <c r="D33">
+        <v>1.67723208132711</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
-        <v>13641.359532800001</v>
+        <v>7348.271956374736</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5">
-        <v>3.2300360000000001</v>
-      </c>
-      <c r="B34" s="5">
-        <v>3.2386149999999998</v>
-      </c>
-      <c r="C34" s="5">
-        <v>3.2386149999999998</v>
-      </c>
-      <c r="D34" s="5">
-        <v>3.0352229999999998</v>
+      <c r="A34">
+        <v>1.7449969918605841</v>
+      </c>
+      <c r="B34">
+        <v>1.7512524033689849</v>
+      </c>
+      <c r="C34">
+        <v>1.7512524033689849</v>
+      </c>
+      <c r="D34">
+        <v>1.6030497303074711</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
-        <v>13127.672652400001</v>
+        <v>7026.2984733408921</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5">
-        <v>3.1094889999999999</v>
-      </c>
-      <c r="B35" s="5">
-        <v>3.117848</v>
-      </c>
-      <c r="C35" s="5">
-        <v>3.117848</v>
-      </c>
-      <c r="D35" s="5">
-        <v>2.9197669999999998</v>
+      <c r="A35">
+        <v>1.6690719806943639</v>
+      </c>
+      <c r="B35">
+        <v>1.675108239976794</v>
+      </c>
+      <c r="C35">
+        <v>1.675108239976794</v>
+      </c>
+      <c r="D35">
+        <v>1.532179731341212</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
-        <v>12633.837124</v>
+        <v>6718.5781744586839</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5">
-        <v>2.9935589999999999</v>
-      </c>
-      <c r="B36" s="5">
-        <v>3.001703</v>
-      </c>
-      <c r="C36" s="5">
-        <v>3.001703</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.8088069999999998</v>
+      <c r="A36">
+        <v>1.5964844572758261</v>
+      </c>
+      <c r="B36">
+        <v>1.602309041289</v>
+      </c>
+      <c r="C36">
+        <v>1.602309041289</v>
+      </c>
+      <c r="D36">
+        <v>1.464471480609665</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
-        <v>12159.048138000002</v>
+        <v>6424.4677170534505</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5">
-        <v>2.8820610000000002</v>
-      </c>
-      <c r="B37" s="5">
-        <v>2.8899949999999999</v>
-      </c>
-      <c r="C37" s="5">
-        <v>2.8899949999999999</v>
-      </c>
-      <c r="D37" s="5">
-        <v>2.7021609999999998</v>
+      <c r="A37">
+        <v>1.527084834289113</v>
+      </c>
+      <c r="B37">
+        <v>1.532704967202984</v>
+      </c>
+      <c r="C37">
+        <v>1.532704967202984</v>
+      </c>
+      <c r="D37">
+        <v>1.399781456893137</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
-        <v>11702.539363600001</v>
+        <v>6143.3538604014084</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5">
-        <v>2.7748170000000001</v>
-      </c>
-      <c r="B38" s="5">
-        <v>2.7825470000000001</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2.7825470000000001</v>
-      </c>
-      <c r="D38" s="5">
-        <v>2.5996540000000001</v>
+      <c r="A38">
+        <v>1.4607304736829909</v>
+      </c>
+      <c r="B38">
+        <v>1.4661531359403981</v>
+      </c>
+      <c r="C38">
+        <v>1.4661531359403981</v>
+      </c>
+      <c r="D38">
+        <v>1.337972866964932</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
-        <v>11263.575067599999</v>
+        <v>5874.6519611645454</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5">
-        <v>2.671659</v>
-      </c>
-      <c r="B39" s="5">
-        <v>2.679189</v>
-      </c>
-      <c r="C39" s="5">
-        <v>2.679189</v>
-      </c>
-      <c r="D39" s="5">
-        <v>2.5011169999999998</v>
+      <c r="A39">
+        <v>1.397285342500856</v>
+      </c>
+      <c r="B39">
+        <v>1.402517279476418</v>
+      </c>
+      <c r="C39">
+        <v>1.402517279476418</v>
+      </c>
+      <c r="D39">
+        <v>1.27891531124942</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="0"/>
-        <v>10841.449650800001</v>
+        <v>5617.8045550435199</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5">
-        <v>2.5724230000000001</v>
-      </c>
-      <c r="B40" s="5">
-        <v>2.579758</v>
-      </c>
-      <c r="C40" s="5">
-        <v>2.579758</v>
-      </c>
-      <c r="D40" s="5">
-        <v>2.406393</v>
+      <c r="A40">
+        <v>1.3366196879146339</v>
+      </c>
+      <c r="B40">
+        <v>1.341667418197545</v>
+      </c>
+      <c r="C40">
+        <v>1.341667418197545</v>
+      </c>
+      <c r="D40">
+        <v>1.2224844680576299</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
-        <v>10435.493211200001</v>
+        <v>5372.2800174296626</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5">
-        <v>2.4769540000000001</v>
-      </c>
-      <c r="B41" s="5">
-        <v>2.4840979999999999</v>
-      </c>
-      <c r="C41" s="5">
-        <v>2.4840979999999999</v>
-      </c>
-      <c r="D41" s="5">
-        <v>2.3153260000000002</v>
+      <c r="A41">
+        <v>1.278609730026053</v>
+      </c>
+      <c r="B41">
+        <v>1.2834795533493799</v>
+      </c>
+      <c r="C41">
+        <v>1.2834795533493799</v>
+      </c>
+      <c r="D41">
+        <v>1.1685617950340179</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
-        <v>10045.0557816</v>
+        <v>5137.5712971895564</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5">
-        <v>2.385103</v>
-      </c>
-      <c r="B42" s="5">
-        <v>2.3920620000000001</v>
-      </c>
-      <c r="C42" s="5">
-        <v>2.3920620000000001</v>
-      </c>
-      <c r="D42" s="5">
-        <v>2.2277719999999999</v>
+      <c r="A42">
+        <v>1.223137371229631</v>
+      </c>
+      <c r="B42">
+        <v>1.227835376069031</v>
+      </c>
+      <c r="C42">
+        <v>1.227835376069031</v>
+      </c>
+      <c r="D42">
+        <v>1.1170342466526131</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
-        <v>9669.5277280000009</v>
+        <v>4913.1947186335274</v>
       </c>
     </row>
   </sheetData>
@@ -6541,770 +6494,771 @@
   <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="2" width="10.83203125" style="1"/>
+    <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="G2" s="8" t="s">
+      <c r="D2" s="6"/>
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1">
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="5">
-        <v>63.152090000000001</v>
+        <v>46.470399999999998</v>
       </c>
       <c r="B3" s="5">
-        <v>70.162809999999993</v>
-      </c>
-      <c r="C3" s="1">
-        <v>63.900727320208567</v>
-      </c>
-      <c r="D3" s="1">
-        <v>70.910980225189363</v>
+        <v>53.477420000000002</v>
+      </c>
+      <c r="C3">
+        <v>47.220086612652928</v>
+      </c>
+      <c r="D3">
+        <v>54.226683992208493</v>
       </c>
       <c r="E3" s="1">
         <f>(A3*0.6*$H$3 + B3*0.34*$H$3) + (A3*0.6*$H$4 + B3*0.34*$H$4)</f>
-        <v>80904.729898538004</v>
-      </c>
-      <c r="G3" s="4" t="s">
+        <v>60357.014699956002</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="2">
         <v>333.77</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1">
+    <row r="4" spans="1:8">
       <c r="A4" s="5">
-        <v>33.210369999999998</v>
+        <v>24.385760000000001</v>
       </c>
       <c r="B4" s="5">
-        <v>36.930489999999999</v>
-      </c>
-      <c r="C4" s="1">
-        <v>33.603148524106167</v>
-      </c>
-      <c r="D4" s="1">
-        <v>37.32290751311853</v>
+        <v>28.08783</v>
+      </c>
+      <c r="C4">
+        <v>24.779059585507969</v>
+      </c>
+      <c r="D4">
+        <v>28.48096923589657</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E42" si="0">(A4*0.6*$H$3 + B4*0.34*$H$3) + (A4*0.6*$H$4 + B4*0.34*$H$4)</f>
-        <v>42560.961364921997</v>
-      </c>
-      <c r="G4" s="4" t="s">
+        <v>31684.055797913999</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <v>976.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1">
+    <row r="5" spans="1:8">
       <c r="A5" s="5">
-        <v>20.8935</v>
+        <v>15.26066</v>
       </c>
       <c r="B5" s="5">
-        <v>23.286359999999998</v>
-      </c>
-      <c r="C5" s="1">
-        <v>21.140600812625689</v>
-      </c>
-      <c r="D5" s="1">
-        <v>23.53321736443587</v>
+        <v>17.616379999999999</v>
+      </c>
+      <c r="C5">
+        <v>15.50765165614907</v>
+      </c>
+      <c r="D5">
+        <v>17.86352691301315</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>26799.558178847998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="1" customFormat="1">
+        <v>19845.303822604001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="5">
-        <v>14.32329</v>
+        <v>10.363300000000001</v>
       </c>
       <c r="B6" s="5">
-        <v>16.02815</v>
-      </c>
-      <c r="C6" s="1">
-        <v>14.492935350439661</v>
-      </c>
-      <c r="D6" s="1">
-        <v>16.19763988757073</v>
+        <v>12.01037</v>
+      </c>
+      <c r="C6">
+        <v>10.53226714795583</v>
+      </c>
+      <c r="D6">
+        <v>12.17979646252749</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>18400.83570715</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="1" customFormat="1">
+        <v>13497.754004565999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="5">
-        <v>10.72648</v>
+        <v>7.6577169999999999</v>
       </c>
       <c r="B7" s="5">
-        <v>12.071709999999999</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10.85394843433976</v>
-      </c>
-      <c r="D7" s="1">
-        <v>12.19909473814894</v>
+        <v>8.9245850000000004</v>
+      </c>
+      <c r="C7">
+        <v>7.7839761080189662</v>
+      </c>
+      <c r="D7">
+        <v>9.051580456240373</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>13810.598786738001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="1" customFormat="1">
+        <v>9996.0355480569997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="5">
-        <v>8.6862010000000005</v>
+        <v>6.1030879999999996</v>
       </c>
       <c r="B8" s="5">
-        <v>9.8416560000000004</v>
-      </c>
-      <c r="C8" s="1">
-        <v>8.7899345006890002</v>
-      </c>
-      <c r="D8" s="1">
-        <v>9.9453711058574328</v>
+        <v>7.1604210000000004</v>
+      </c>
+      <c r="C8">
+        <v>6.2051275630870144</v>
+      </c>
+      <c r="D8">
+        <v>7.2634521419054652</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>11213.138196982802</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="1" customFormat="1">
+        <v>7987.9247083037999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="5">
-        <v>7.4685389999999998</v>
+        <v>5.1597460000000002</v>
       </c>
       <c r="B9" s="5">
-        <v>8.5222680000000004</v>
-      </c>
-      <c r="C9" s="1">
-        <v>7.5582661145030512</v>
-      </c>
-      <c r="D9" s="1">
-        <v>8.6120355387079801</v>
+        <v>6.096686</v>
+      </c>
+      <c r="C9">
+        <v>5.2473315178480444</v>
+      </c>
+      <c r="D9">
+        <v>6.1854977100182351</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>9668.0820687203995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="1" customFormat="1">
+        <v>6772.4198550268002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5">
-        <v>6.6901799999999998</v>
+        <v>4.5454090000000003</v>
       </c>
       <c r="B10" s="5">
-        <v>7.687729</v>
-      </c>
-      <c r="C10" s="1">
-        <v>6.7710778020720523</v>
-      </c>
-      <c r="D10" s="1">
-        <v>7.7687210864331533</v>
+        <v>5.4086730000000003</v>
+      </c>
+      <c r="C10">
+        <v>4.6237521159820103</v>
+      </c>
+      <c r="D10">
+        <v>5.4884547877412944</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>8684.3855192821993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="1" customFormat="1">
+        <v>5982.9473006394001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="5">
-        <v>6.149851</v>
+        <v>4.1115380000000004</v>
       </c>
       <c r="B11" s="5">
-        <v>7.1146130000000003</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6.224705244567299</v>
-      </c>
-      <c r="D11" s="1">
-        <v>7.1896137207144859</v>
+        <v>4.9256779999999996</v>
+      </c>
+      <c r="C11">
+        <v>4.1834588234507448</v>
+      </c>
+      <c r="D11">
+        <v>4.9992308903273681</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>8004.2809135354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="1" customFormat="1">
+        <v>5426.6840955964008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="5">
-        <v>5.7414199999999997</v>
+        <v>3.7795640000000001</v>
       </c>
       <c r="B12" s="5">
-        <v>6.685238</v>
-      </c>
-      <c r="C12" s="1">
-        <v>5.8117613564356772</v>
-      </c>
-      <c r="D12" s="1">
-        <v>6.755776140247197</v>
+        <v>4.5575359999999998</v>
+      </c>
+      <c r="C12">
+        <v>3.84662230863943</v>
+      </c>
+      <c r="D12">
+        <v>4.6264026356160599</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="0"/>
-        <v>7491.9049400883996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="1" customFormat="1">
+        <v>5001.6945095727997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="5">
-        <v>5.4086860000000003</v>
+        <v>3.5076779999999999</v>
       </c>
       <c r="B13" s="5">
-        <v>6.3373910000000002</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5.4753786039796397</v>
-      </c>
-      <c r="D13" s="1">
-        <v>6.404328095623204</v>
+        <v>4.2563719999999998</v>
+      </c>
+      <c r="C13">
+        <v>3.5707657934000001</v>
+      </c>
+      <c r="D13">
+        <v>4.3214288207571387</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>7075.3591270258003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="1" customFormat="1">
+        <v>4653.7819755855999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="5">
-        <v>5.1217100000000002</v>
+        <v>3.2734350000000001</v>
       </c>
       <c r="B14" s="5">
-        <v>6.0380159999999998</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5.1852652332437366</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6.1018622291019176</v>
+        <v>3.9965760000000001</v>
+      </c>
+      <c r="C14">
+        <v>3.333091007905495</v>
+      </c>
+      <c r="D14">
+        <v>4.0583449483533469</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>6716.3803932888004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="1" customFormat="1">
+        <v>4353.8920425468004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="5">
-        <v>4.864395</v>
+        <v>3.0646200000000001</v>
       </c>
       <c r="B15" s="5">
-        <v>5.7694179999999999</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4.9251365337539994</v>
-      </c>
-      <c r="D15" s="1">
-        <v>5.8304943420248936</v>
+        <v>3.764284</v>
+      </c>
+      <c r="C15">
+        <v>3.1211921629413131</v>
+      </c>
+      <c r="D15">
+        <v>3.823098818291518</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>6394.4309117623998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="1" customFormat="1">
+        <v>4086.2454433112002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="5">
-        <v>4.6279570000000003</v>
+        <v>2.8744350000000001</v>
       </c>
       <c r="B16" s="5">
-        <v>5.5220050000000001</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4.6861047051275726</v>
-      </c>
-      <c r="D16" s="1">
-        <v>5.5805299148887313</v>
+        <v>3.551847</v>
+      </c>
+      <c r="C16">
+        <v>2.9281672723631171</v>
+      </c>
+      <c r="D16">
+        <v>3.6079386711567829</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>6098.3318780930003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="1" customFormat="1">
+        <v>3842.0902818245995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="5">
-        <v>4.4074790000000004</v>
+        <v>2.6989610000000002</v>
       </c>
       <c r="B17" s="5">
-        <v>5.2904669999999996</v>
-      </c>
-      <c r="C17" s="1">
-        <v>4.4631981788375041</v>
-      </c>
-      <c r="D17" s="1">
-        <v>5.3466042926715147</v>
+        <v>3.354914</v>
+      </c>
+      <c r="C17">
+        <v>2.750040910481085</v>
+      </c>
+      <c r="D17">
+        <v>3.4084562134609611</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>5821.8521722686</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="1" customFormat="1">
+        <v>3616.4072543872003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="5">
-        <v>4.2001049999999998</v>
+        <v>2.5358230000000002</v>
       </c>
       <c r="B18" s="5">
-        <v>5.0717699999999999</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4.2535270472230744</v>
-      </c>
-      <c r="D18" s="1">
-        <v>5.1256493651793233</v>
+        <v>3.1708919999999998</v>
+      </c>
+      <c r="C18">
+        <v>2.5844038791825601</v>
+      </c>
+      <c r="D18">
+        <v>3.2220268392555962</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
-        <v>5561.3948934959999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="1" customFormat="1">
+        <v>3406.1740660116002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="5">
-        <v>4.0040760000000004</v>
+        <v>2.3834789999999999</v>
       </c>
       <c r="B19" s="5">
-        <v>4.8640879999999997</v>
-      </c>
-      <c r="C19" s="1">
-        <v>4.0553151725183652</v>
-      </c>
-      <c r="D19" s="1">
-        <v>4.9158215276778678</v>
+        <v>2.9981360000000001</v>
+      </c>
+      <c r="C19">
+        <v>2.4296941871439279</v>
+      </c>
+      <c r="D19">
+        <v>3.046985879802667</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
-        <v>5314.7637147904006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="1" customFormat="1">
+        <v>3209.4456208828001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="5">
-        <v>3.8182309999999999</v>
+        <v>2.240847</v>
       </c>
       <c r="B20" s="5">
-        <v>4.6662480000000004</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3.8673889015587428</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4.7159358749026223</v>
+        <v>2.835518</v>
+      </c>
+      <c r="C20">
+        <v>2.284816246294668</v>
+      </c>
+      <c r="D20">
+        <v>2.8821928530898759</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
-        <v>5080.5233401884007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="1" customFormat="1">
+        <v>3024.8687769664002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="5">
-        <v>3.6417380000000001</v>
+        <v>2.1071029999999999</v>
       </c>
       <c r="B21" s="5">
-        <v>4.4774349999999998</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3.6889064682886259</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4.5251671197617469</v>
+        <v>2.6821999999999999</v>
+      </c>
+      <c r="C21">
+        <v>2.148938555571438</v>
+      </c>
+      <c r="D21">
+        <v>2.7268003711345541</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
-        <v>4857.6566070890003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="1" customFormat="1">
+        <v>2851.4224146460001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="5">
-        <v>3.473948</v>
+        <v>1.9815799999999999</v>
       </c>
       <c r="B22" s="5">
-        <v>4.2970280000000001</v>
-      </c>
-      <c r="C22" s="1">
-        <v>3.519214337760677</v>
-      </c>
-      <c r="D22" s="1">
-        <v>4.3428911112182549</v>
+        <v>2.5375100000000002</v>
+      </c>
+      <c r="C22">
+        <v>2.0213856495310458</v>
+      </c>
+      <c r="D22">
+        <v>2.5801310689954891</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
-        <v>4645.3766459464005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="1" customFormat="1">
+        <v>2688.282793378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="5">
-        <v>3.314324</v>
+        <v>1.863707</v>
       </c>
       <c r="B23" s="5">
-        <v>4.1245279999999998</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3.3577705469749781</v>
-      </c>
-      <c r="D23" s="1">
-        <v>4.1686005095444001</v>
+        <v>2.400881</v>
+      </c>
+      <c r="C23">
+        <v>1.901579884476253</v>
+      </c>
+      <c r="D23">
+        <v>2.441611600048994</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
-        <v>4443.038987358399</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="1" customFormat="1">
+        <v>2534.7484208097999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="5">
-        <v>3.162401</v>
+        <v>1.752977</v>
       </c>
       <c r="B24" s="5">
-        <v>3.9595020000000001</v>
-      </c>
-      <c r="C24" s="1">
-        <v>3.2041034411521019</v>
-      </c>
-      <c r="D24" s="1">
-        <v>4.0018596073527801</v>
+        <v>2.2718120000000002</v>
+      </c>
+      <c r="C24">
+        <v>1.7890096173892831</v>
+      </c>
+      <c r="D24">
+        <v>2.3107368192875271</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
-        <v>4250.0851680455999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" s="1" customFormat="1">
+        <v>2390.1975214156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="5">
-        <v>3.0177559999999999</v>
+        <v>1.64893</v>
       </c>
       <c r="B25" s="5">
-        <v>3.8015639999999999</v>
-      </c>
-      <c r="C25" s="1">
-        <v>3.057789140172817</v>
-      </c>
-      <c r="D25" s="1">
-        <v>3.8422798413734589</v>
+        <v>2.149851</v>
+      </c>
+      <c r="C25">
+        <v>1.683211399970115</v>
+      </c>
+      <c r="D25">
+        <v>2.187049970990036</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
-        <v>4066.0106816471998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="1" customFormat="1">
+        <v>2254.0670983818</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="5">
-        <v>2.8800059999999998</v>
+        <v>1.5511459999999999</v>
       </c>
       <c r="B26" s="5">
-        <v>3.6503649999999999</v>
-      </c>
-      <c r="C26" s="1">
-        <v>2.9184389428289941</v>
-      </c>
-      <c r="D26" s="1">
-        <v>3.6895062635545579</v>
+        <v>2.0345810000000002</v>
+      </c>
+      <c r="C26">
+        <v>1.5837596487912859</v>
+      </c>
+      <c r="D26">
+        <v>2.0701313920114468</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
-        <v>3890.3589514789992</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="1" customFormat="1">
+        <v>2125.8411935878003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="5">
-        <v>2.748793</v>
+        <v>1.459236</v>
       </c>
       <c r="B27" s="5">
-        <v>3.5055779999999999</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2.7856920273276269</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3.5432098374926402</v>
+        <v>1.9256180000000001</v>
+      </c>
+      <c r="C27">
+        <v>1.490260333761408</v>
+      </c>
+      <c r="D27">
+        <v>1.9595917735929289</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
-        <v>3722.7028557264002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="1" customFormat="1">
+        <v>2005.0429211644</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="5">
-        <v>2.6237819999999998</v>
+        <v>1.372835</v>
       </c>
       <c r="B28" s="5">
-        <v>3.3668990000000001</v>
-      </c>
-      <c r="C28" s="1">
-        <v>2.659210995437812</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3.4030828496250791</v>
+        <v>1.8226</v>
+      </c>
+      <c r="C28">
+        <v>1.4023468536022581</v>
+      </c>
+      <c r="D28">
+        <v>1.8550678881300231</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
-        <v>3562.6436006121999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="1" customFormat="1">
+        <v>1891.2240639500001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="5">
-        <v>2.5046590000000002</v>
+        <v>1.2916049999999999</v>
       </c>
       <c r="B29" s="5">
-        <v>3.2340399999999998</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2.5386789623681518</v>
-      </c>
-      <c r="D29" s="1">
-        <v>3.2688360024033609</v>
+        <v>1.7251920000000001</v>
+      </c>
+      <c r="C29">
+        <v>1.319677126014549</v>
+      </c>
+      <c r="D29">
+        <v>1.756219671001219</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="0"/>
-        <v>3409.80602963</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="1" customFormat="1">
+        <v>1783.9696594356001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="5">
-        <v>2.3911289999999998</v>
+        <v>1.215231</v>
       </c>
       <c r="B30" s="5">
-        <v>3.106732</v>
-      </c>
-      <c r="C30" s="1">
-        <v>2.423797503816937</v>
-      </c>
-      <c r="D30" s="1">
-        <v>3.1401964305998722</v>
+        <v>1.6330769999999999</v>
+      </c>
+      <c r="C30">
+        <v>1.2419313740904601</v>
+      </c>
+      <c r="D30">
+        <v>1.6627280670635161</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
-        <v>3263.8383876955995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="1" customFormat="1">
+        <v>1682.8908456906001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="5">
-        <v>2.2829120000000001</v>
+        <v>1.143416</v>
       </c>
       <c r="B31" s="5">
-        <v>2.9847190000000001</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2.3142850934043979</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3.0169062375487008</v>
+        <v>1.5459590000000001</v>
+      </c>
+      <c r="C31">
+        <v>1.168810330627077</v>
+      </c>
+      <c r="D31">
+        <v>1.5742933259976339</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="0"/>
-        <v>3124.4065035482004</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="1" customFormat="1">
+        <v>1587.6222670282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="5">
-        <v>2.1797460000000002</v>
+        <v>1.0758829999999999</v>
       </c>
       <c r="B32" s="5">
-        <v>2.8677609999999998</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2.2098758337527191</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2.898721335909983</v>
+        <v>1.463557</v>
+      </c>
+      <c r="C32">
+        <v>1.1000337091571499</v>
+      </c>
+      <c r="D32">
+        <v>1.490633575990699</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
-        <v>2991.1974847117999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="1" customFormat="1">
+        <v>1497.8209733785998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="5">
-        <v>2.0813809999999999</v>
+        <v>1.012372</v>
       </c>
       <c r="B33" s="5">
-        <v>2.755627</v>
-      </c>
-      <c r="C33" s="1">
-        <v>2.1103183745006651</v>
-      </c>
-      <c r="D33" s="1">
-        <v>2.7854104768527841</v>
+        <v>1.38561</v>
+      </c>
+      <c r="C33">
+        <v>1.03533885806614</v>
+      </c>
+      <c r="D33">
+        <v>1.411483582298672</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
-        <v>2863.9118820805998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="1" customFormat="1">
+        <v>1413.1662892619997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="5">
-        <v>1.987581</v>
+        <v>0.95264000000000004</v>
       </c>
       <c r="B34" s="5">
-        <v>2.6480999999999999</v>
-      </c>
-      <c r="C34" s="1">
-        <v>2.01537495829758</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2.6767544041281801</v>
+        <v>1.3118700000000001</v>
+      </c>
+      <c r="C34">
+        <v>0.97447955017993115</v>
+      </c>
+      <c r="D34">
+        <v>1.3365936382240211</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
-        <v>2742.2674897019997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="1" customFormat="1">
+        <v>1333.3566953459999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="5">
-        <v>1.8981239999999999</v>
+        <v>0.89645900000000001</v>
       </c>
       <c r="B35" s="5">
-        <v>2.5449760000000001</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1.9248205612632321</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2.5725450974594821</v>
+        <v>1.2421040000000001</v>
+      </c>
+      <c r="C35">
+        <v>0.91722487953434495</v>
+      </c>
+      <c r="D35">
+        <v>1.2657285579724331</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
-        <v>2625.9988992848002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="1" customFormat="1">
+        <v>1258.1091471052</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="5">
-        <v>1.812799</v>
+        <v>0.84361399999999998</v>
       </c>
       <c r="B36" s="5">
-        <v>2.4460570000000001</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1.83844210806302</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2.4725850846074402</v>
+        <v>1.176094</v>
+      </c>
+      <c r="C36">
+        <v>0.86335824755649071</v>
+      </c>
+      <c r="D36">
+        <v>1.1986667527058541</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
-        <v>2514.8520232706005</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="1" customFormat="1">
+        <v>1187.1575024971999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="5">
-        <v>1.731406</v>
+        <v>0.79390499999999997</v>
       </c>
       <c r="B37" s="5">
-        <v>2.351159</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1.7560377491213519</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2.3766868094986648</v>
+        <v>1.113632</v>
+      </c>
+      <c r="C37">
+        <v>0.81267642666704865</v>
+      </c>
+      <c r="D37">
+        <v>1.135199377572446</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
-        <v>2408.5876587681996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="1" customFormat="1">
+        <v>1120.2518668276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="5">
-        <v>1.6537539999999999</v>
+        <v>0.747143</v>
       </c>
       <c r="B38" s="5">
-        <v>2.2601059999999999</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.6774161916082071</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2.2846720482120682</v>
+        <v>1.0545230000000001</v>
+      </c>
+      <c r="C38">
+        <v>0.7649886926283358</v>
+      </c>
+      <c r="D38">
+        <v>1.075129541154316</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
-        <v>2306.9772422788001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="1" customFormat="1">
+        <v>1057.1567845774</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="5">
-        <v>1.5796650000000001</v>
+        <v>0.703152</v>
       </c>
       <c r="B39" s="5">
-        <v>2.1727280000000002</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1.6023960781261051</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2.196371367070876</v>
+        <v>0.998583</v>
+      </c>
+      <c r="C39">
+        <v>0.72011601890042221</v>
+      </c>
+      <c r="D39">
+        <v>1.018271570868047</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="0"/>
-        <v>2209.8051033604002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="1" customFormat="1">
+        <v>997.65192074339996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="5">
-        <v>1.508969</v>
+        <v>0.66176500000000005</v>
       </c>
       <c r="B40" s="5">
-        <v>2.088867</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1.530805408407365</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2.111623618497811</v>
+        <v>0.94564099999999995</v>
+      </c>
+      <c r="C40">
+        <v>0.67789032748534817</v>
+      </c>
+      <c r="D40">
+        <v>0.96445032913927042</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
-        <v>2116.8672067686002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="1" customFormat="1">
+        <v>941.52980717380001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="5">
-        <v>1.4415020000000001</v>
+        <v>0.62282700000000002</v>
       </c>
       <c r="B41" s="5">
-        <v>2.0083709999999999</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1.4624810001777599</v>
-      </c>
-      <c r="D41" s="1">
-        <v>2.0302754711721178</v>
+        <v>0.89553099999999997</v>
+      </c>
+      <c r="C41">
+        <v>0.63815379156172958</v>
+      </c>
+      <c r="D41">
+        <v>0.91350057601830292</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
-        <v>2027.9669071818003</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="1" customFormat="1">
+        <v>888.59463711980004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="5">
-        <v>1.3771139999999999</v>
+        <v>0.58619100000000002</v>
       </c>
       <c r="B42" s="5">
-        <v>1.9310959999999999</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1.3972679859049131</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1.952180971554526</v>
+        <v>0.84809900000000005</v>
+      </c>
+      <c r="C42">
+        <v>0.60075818577385576</v>
+      </c>
+      <c r="D42">
+        <v>0.86526637445876275</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
-        <v>1942.9221294807999</v>
+        <v>838.6622390302</v>
       </c>
     </row>
   </sheetData>
@@ -7322,7 +7276,7 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.83203125"/>
     <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10.83203125" style="1"/>
     <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -7330,13 +7284,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7346,486 +7300,486 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>53.062509524530469</v>
-      </c>
-      <c r="B3" s="1">
-        <v>43.433011902723912</v>
+      <c r="A3">
+        <v>36.3875035436673</v>
+      </c>
+      <c r="B3">
+        <v>26.762737099718681</v>
       </c>
       <c r="C3" s="1">
         <f>A3*0.57*$G$3 + B3*0.3*$G$3</f>
-        <v>664625.65116892126</v>
-      </c>
-      <c r="G3" s="6">
+        <v>441845.02418472001</v>
+      </c>
+      <c r="G3" s="3">
         <v>15358</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>27.86542293427128</v>
-      </c>
-      <c r="B4" s="1">
-        <v>22.78124305828052</v>
+      <c r="A4">
+        <v>19.068667698604539</v>
+      </c>
+      <c r="B4">
+        <v>14.008246040620829</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C42" si="0">A4*0.57*$G$3 + B4*0.3*$G$3</f>
-        <v>348897.88355870848</v>
+        <v>231469.85396120243</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>17.47107172870497</v>
-      </c>
-      <c r="B5" s="1">
-        <v>14.24062824495023</v>
+      <c r="A5">
+        <v>11.89391140140968</v>
+      </c>
+      <c r="B5">
+        <v>8.7118291153337282</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
-        <v>218555.08075317071</v>
+        <v>144258.89550861303</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>11.904452580000809</v>
-      </c>
-      <c r="B6" s="1">
-        <v>9.6513831730465913</v>
+      <c r="A6">
+        <v>8.0297994392610352</v>
+      </c>
+      <c r="B6">
+        <v>5.8506941964034276</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
-        <v>148680.07498397675</v>
+        <v>97249.834519766591</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>8.8387961588901902</v>
-      </c>
-      <c r="B7" s="1">
-        <v>7.1115549898859776</v>
+      <c r="A7">
+        <v>5.8843580348675601</v>
+      </c>
+      <c r="B7">
+        <v>4.2554936529769947</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>110141.13036309491</v>
+        <v>71118.784755438915</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>7.0849087909593083</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5.6486998305381819</v>
+      <c r="A8">
+        <v>4.6433772775092166</v>
+      </c>
+      <c r="B8">
+        <v>3.3278808875219901</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>88047.536249806857</v>
+        <v>55981.281691121148</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>6.0264281223570793</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4.7584754897786086</v>
+      <c r="A9">
+        <v>3.8843641880636381</v>
+      </c>
+      <c r="B9">
+        <v>2.7571334922254209</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>74679.913340407176</v>
+        <v>46707.174016239776</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>5.3411416541168917</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4.1769848700221246</v>
+      <c r="A10">
+        <v>3.3860856411064</v>
+      </c>
+      <c r="B10">
+        <v>2.380363381338308</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>66001.714598778446</v>
+        <v>40609.283110562013</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>4.8596375944339529</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3.76529097599825</v>
+      <c r="A11">
+        <v>3.0319420110133901</v>
+      </c>
+      <c r="B11">
+        <v>2.1115822163414562</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
-        <v>59889.760722744832</v>
+        <v>36270.706184503499</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>4.4924166846615314</v>
-      </c>
-      <c r="B12" s="1">
-        <v>3.449847368165516</v>
+      <c r="A12">
+        <v>2.760112889734557</v>
+      </c>
+      <c r="B12">
+        <v>1.905089267928735</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
-        <v>55221.711966613919</v>
+        <v>32939.702136564549</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>4.1919430052406739</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3.1914703850355628</v>
+      <c r="A13">
+        <v>2.537581206453964</v>
+      </c>
+      <c r="B13">
+        <v>1.7363861301347849</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
-        <v>51400.901236470017</v>
+        <v>30214.363592153393</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>3.9327759314330142</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2.96908683430234</v>
+      <c r="A14">
+        <v>2.346521966988353</v>
+      </c>
+      <c r="B14">
+        <v>1.5921706449096149</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
-        <v>48107.527150685084</v>
+        <v>27877.36111969062</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>3.7011347939835422</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2.7711930759089451</v>
+      <c r="A15">
+        <v>2.177146238647798</v>
+      </c>
+      <c r="B15">
+        <v>1.465073045596673</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
-        <v>45167.951032562436</v>
+        <v>25809.046352179255</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>3.4894071691504198</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2.5913574905424501</v>
+      <c r="A16">
+        <v>2.023931077048621</v>
+      </c>
+      <c r="B16">
+        <v>1.3508807691005651</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
-        <v>42485.900225098201</v>
+        <v>23941.662139902193</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1">
-        <v>3.2932549707774679</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2.4258487440299632</v>
+      <c r="A17">
+        <v>1.883630267823037</v>
+      </c>
+      <c r="B17">
+        <v>1.247072859458314</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
-        <v>40006.207112727847</v>
+        <v>22235.175875007171</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="1">
-        <v>3.1100877845372801</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2.2723834599484478</v>
+      <c r="A18">
+        <v>1.754223183421407</v>
+      </c>
+      <c r="B18">
+        <v>1.1520446333541181</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
-        <v>37695.6746244729</v>
+        <v>20664.505444777766</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="1">
-        <v>2.9382564983119668</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2.129463951340786</v>
+      <c r="A19">
+        <v>1.634358342797616</v>
+      </c>
+      <c r="B19">
+        <v>1.0646965640473289</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
-        <v>35532.965891020394</v>
+        <v>19212.753943542561</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="1">
-        <v>2.7766266664643329</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1.9960272152887011</v>
+      <c r="A20">
+        <v>1.5230580529971389</v>
+      </c>
+      <c r="B20">
+        <v>0.98421551402933005</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
-        <v>33503.252227549921</v>
+        <v>17867.616138758865</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="1">
-        <v>2.6243521880219109</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1.871258236371238</v>
+      <c r="A21">
+        <v>1.4195609450136</v>
+      </c>
+      <c r="B21">
+        <v>0.90995764391862133</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="0"/>
-        <v>31595.37171333193</v>
+        <v>16619.460534896411</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="1">
-        <v>2.4807547239934329</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1.7544900972780131</v>
+      <c r="A22">
+        <v>1.323237411663039</v>
+      </c>
+      <c r="B22">
+        <v>0.84138513492229094</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="0"/>
-        <v>29800.313373320667</v>
+        <v>15460.297566583904</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="1">
-        <v>2.3452589820103831</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.645150005640033</v>
+      <c r="A23">
+        <v>1.23354364309777</v>
+      </c>
+      <c r="B23">
+        <v>0.77803144773856536</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="0"/>
-        <v>28110.401980043698</v>
+        <v>14383.21715660713</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="1">
-        <v>2.217357559798705</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1.542729653545067</v>
+      <c r="A24">
+        <v>1.1499961451016441</v>
+      </c>
+      <c r="B24">
+        <v>0.7194817615399719</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="0"/>
-        <v>26518.853725674991</v>
+        <v>13382.075522107763</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="1">
-        <v>2.09659146339534</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1.446768511571709</v>
+      <c r="A25">
+        <v>1.072157168926988</v>
+      </c>
+      <c r="B25">
+        <v>0.66536153052784164</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="0"/>
-        <v>25019.528706266101</v>
+        <v>12451.314901970965</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="1">
-        <v>1.982538968839717</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.356844033844794</v>
+      <c r="A26">
+        <v>0.99962599136260621</v>
+      </c>
+      <c r="B26">
+        <v>0.61532941950676923</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="0"/>
-        <v>23606.788287097515</v>
+        <v>11585.854673383225</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="1">
-        <v>1.8748089529901999</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.272565587475109</v>
+      <c r="A27">
+        <v>0.93203336506799417</v>
+      </c>
+      <c r="B27">
+        <v>0.56907263596316204</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="0"/>
-        <v>22275.408750746206</v>
+        <v>10781.021262743798</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="1">
-        <v>1.773036643353445</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.193570417642841</v>
+      <c r="A28">
+        <v>0.86903771709932676</v>
+      </c>
+      <c r="B28">
+        <v>0.52630360426153311</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="0"/>
-        <v>21020.525500362281</v>
+        <v>10032.499544025119</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="1">
-        <v>1.6768806998038359</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.119520750817675</v>
+      <c r="A29">
+        <v>0.81032233834153544</v>
+      </c>
+      <c r="B29">
+        <v>0.48675741843516579</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="0"/>
-        <v>19837.594166242121</v>
+        <v>9336.2964988802833</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="1">
-        <v>1.5860210497056171</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0501015568540779</v>
+      <c r="A30">
+        <v>0.75559315816859396</v>
+      </c>
+      <c r="B30">
+        <v>0.45018976993530663</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="0"/>
-        <v>18722.361343435434</v>
+        <v>8688.7121881972926</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="1">
-        <v>1.500157166813243</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.98501871202229074</v>
+      <c r="A31">
+        <v>0.70457688488469239</v>
+      </c>
+      <c r="B31">
+        <v>0.41637518452302419</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="0"/>
-        <v>17670.841061484636</v>
+        <v>8086.3153500650715</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="1">
-        <v>1.4190066266299231</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.92399742234108828</v>
+      <c r="A32">
+        <v>0.65701939131154086</v>
+      </c>
+      <c r="B32">
+        <v>0.38510547580053373</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="0"/>
-        <v>16679.294873610273</v>
+        <v>7525.9221419080859</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1">
-        <v>1.342303846384209</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.86678082894297381</v>
+      <c r="A33">
+        <v>0.61268427753662047</v>
+      </c>
+      <c r="B33">
+        <v>0.35618836203803989</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="0"/>
-        <v>15744.214400750005</v>
+        <v>7004.577185866292</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="1">
-        <v>1.269798957960814</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.81312875049657407</v>
+      <c r="A34">
+        <v>0.57135157101184098</v>
+      </c>
+      <c r="B34">
+        <v>0.32944621406007002</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" si="0"/>
-        <v>14862.305670964359</v>
+        <v>6519.5364203922818</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="1">
-        <v>1.2012567836116761</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.76281653564100316</v>
+      <c r="A35">
+        <v>0.5328165394394091</v>
+      </c>
+      <c r="B35">
+        <v>0.30471491345979967</v>
       </c>
       <c r="C35" s="1">
         <f t="shared" si="0"/>
-        <v>14030.474865455984</v>
+        <v>6068.2514475196331</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="1">
-        <v>1.136455895917232</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.71563400814118461</v>
+      <c r="A36">
+        <v>0.4968886002591783</v>
+      </c>
+      <c r="B36">
+        <v>0.28184280681329221</v>
       </c>
       <c r="C36" s="1">
         <f t="shared" si="0"/>
-        <v>13245.815229322896</v>
+        <v>5648.3551680964247</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="1">
-        <v>1.0751877498112661</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.67138449290923086</v>
+      <c r="A37">
+        <v>0.46339031523977309</v>
+      </c>
+      <c r="B37">
+        <v>0.26068974525142607</v>
       </c>
       <c r="C37" s="1">
         <f t="shared" si="0"/>
-        <v>12505.5949857428</v>
+        <v>5257.6485552993081</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="1">
-        <v>1.0172558780901371</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.62988391413315037</v>
+      <c r="A38">
+        <v>0.43215646143054198</v>
+      </c>
+      <c r="B38">
+        <v>0.24112620095352591</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" si="0"/>
-        <v>11807.24613813082</v>
+        <v>4894.0884510239248</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="1">
-        <v>0.96247514389447508</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.59095995863300266</v>
+      <c r="A39">
+        <v>0.40303317141089212</v>
+      </c>
+      <c r="B39">
+        <v>0.22303245354369489</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" si="0"/>
-        <v>11148.354071566564</v>
+        <v>4555.7762909784542</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="1">
-        <v>0.91067104492854634</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.55445129872243137</v>
+      <c r="A40">
+        <v>0.37587713685799429</v>
+      </c>
+      <c r="B40">
+        <v>0.20629784032809559</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" si="0"/>
-        <v>10526.64788130092</v>
+        <v>4240.9476782107604</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1">
-        <v>0.86167906502424307</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.52020686966792573</v>
+      <c r="A41">
+        <v>0.3505548702448304</v>
+      </c>
+      <c r="B41">
+        <v>0.1908200650213748</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" si="0"/>
-        <v>9939.9913672741259</v>
+        <v>3947.9627349949419</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="1">
-        <v>0.8153440692088102</v>
-      </c>
-      <c r="B42" s="1">
-        <v>0.4880851974173292</v>
+      <c r="A42">
+        <v>0.32694202002328632</v>
+      </c>
+      <c r="B42">
+        <v>0.17650456016833499</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" si="0"/>
-        <v>9386.3746410786789</v>
+        <v>3675.2971703246367</v>
       </c>
     </row>
   </sheetData>
@@ -7838,7 +7792,7 @@
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125"/>
     <col min="2" max="2" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10.83203125" style="1"/>
     <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -7846,10 +7800,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7859,366 +7813,366 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>51.074503035747803</v>
+      <c r="A3">
+        <v>34.400528382781509</v>
       </c>
       <c r="B3" s="1">
         <f>A3*0.8645*$F$3</f>
-        <v>427321.52040848171</v>
-      </c>
-      <c r="F3" s="6">
+        <v>287816.52718375967</v>
+      </c>
+      <c r="F3" s="3">
         <v>9678</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>26.81470673897185</v>
+      <c r="A4">
+        <v>18.02293083448231</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B42" si="0">A4*0.8645*$F$3</f>
-        <v>224348.7566581908</v>
+        <v>150791.21183063556</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>16.801833720652109</v>
+      <c r="A5">
+        <v>11.23477422464107</v>
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>140574.74286405326</v>
+        <v>93997.210305882953</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>11.435740780726761</v>
+      <c r="A6">
+        <v>7.5765567215025804</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>95678.623323992724</v>
+        <v>63390.254339381856</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>8.4774411748616672</v>
+      <c r="A7">
+        <v>5.5436354589102548</v>
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>70927.622134274046</v>
+        <v>46381.552283217759</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>6.7825215011866931</v>
+      <c r="A8">
+        <v>4.3663933135922406</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>56746.854649995126</v>
+        <v>36532.001655693559</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>5.7577549376913408</v>
+      <c r="A9">
+        <v>3.645415483456266</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>48173.010952091441</v>
+        <v>30499.846191765184</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="1">
-        <v>5.092967058969009</v>
+      <c r="A10">
+        <v>3.1715072768284589</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>42610.976077548941</v>
+        <v>26534.831099038569</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="1">
-        <v>4.6250327431972709</v>
+      <c r="A11">
+        <v>2.8343786680002978</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>38695.942325249329</v>
+        <v>23714.200429430002</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="1">
-        <v>4.2677404239036791</v>
+      <c r="A12">
+        <v>2.575526718620031</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>35706.609330585663</v>
+        <v>21548.481685334631</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="1">
-        <v>3.9752728921947762</v>
+      <c r="A13">
+        <v>2.3636832879427678</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>33259.641413296471</v>
+        <v>19776.065871083887</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="1">
-        <v>3.7230860375087742</v>
+      <c r="A14">
+        <v>2.1819483186452171</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>31149.687057088075</v>
+        <v>18255.556443174952</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="1">
-        <v>3.4978646349603268</v>
+      <c r="A15">
+        <v>2.0210244280247451</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>29265.342688662753</v>
+        <v>16909.165631269101</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="1">
-        <v>3.2922358145117792</v>
+      <c r="A16">
+        <v>1.875652117498926</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>27544.922225004506</v>
+        <v>15692.889151482157</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1">
-        <v>3.1019828736116422</v>
+      <c r="A17">
+        <v>1.742728508014423</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>25953.146071828251</v>
+        <v>14580.766359737221</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1">
-        <v>2.924575179747043</v>
+      <c r="A18">
+        <v>1.620313039471607</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>24468.841360702179</v>
+        <v>13556.561305747371</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1">
-        <v>2.7583914995008652</v>
+      <c r="A19">
+        <v>1.5071009555071699</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>23078.443829860425</v>
+        <v>12609.357574475909</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1">
-        <v>2.602308940989758</v>
+      <c r="A20">
+        <v>1.40214369765323</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>21772.558657262081</v>
+        <v>11731.218927240141</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1">
-        <v>2.4554847883036168</v>
+      <c r="A21">
+        <v>1.3046997294535649</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>20544.135149849481</v>
+        <v>10915.94120213781</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1">
-        <v>2.3172401743229991</v>
+      <c r="A22">
+        <v>1.214154330875137</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>19387.493476936208</v>
+        <v>10158.381263484178</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1">
-        <v>2.186997571519484</v>
+      <c r="A23">
+        <v>1.1299759195356149</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>18297.801678799635</v>
+        <v>9454.0915576401821</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1">
-        <v>2.064246765870303</v>
+      <c r="A24">
+        <v>1.051691764397011</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>17270.790982980219</v>
+        <v>8799.116918448728</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1">
-        <v>1.9485259418142391</v>
+      <c r="A25">
+        <v>0.97887403737784473</v>
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>16302.597549087212</v>
+        <v>8189.877866220635</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1">
-        <v>1.8394108161993989</v>
+      <c r="A26">
+        <v>0.91113141386210827</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>15389.671556549194</v>
+        <v>7623.1003322925453</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1">
-        <v>1.736508088380073</v>
+      <c r="A27">
+        <v>0.84810368561347127</v>
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>14528.722403991458</v>
+        <v>7095.7705872679226</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1">
-        <v>1.6394512306581011</v>
+      <c r="A28">
+        <v>0.78945803959364014</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>13716.68348941222</v>
+        <v>6605.104107263378</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1">
-        <v>1.5478975709200169</v>
+      <c r="A29">
+        <v>0.73488628517808274</v>
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>12950.687801684111</v>
+        <v>6148.5223750457881</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1">
-        <v>1.4615261093557119</v>
+      <c r="A30">
+        <v>0.68410264499615414</v>
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>12228.04965384489</v>
+        <v>5723.6343968068186</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1">
-        <v>1.3800357702410011</v>
+      <c r="A31">
+        <v>0.63684190090410198</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>11546.250056407238</v>
+        <v>5328.2211902031877</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1">
-        <v>1.3031439269297851</v>
+      <c r="A32">
+        <v>0.59285778017758639</v>
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>10902.924376512476</v>
+        <v>4960.2222822249805</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1">
-        <v>1.230585111000319</v>
+      <c r="A33">
+        <v>0.55192151688140234</v>
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>10295.851537833711</v>
+        <v>4617.7236727069649</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1">
-        <v>1.1621098552487701</v>
+      <c r="A34">
+        <v>0.51382055011247019</v>
       </c>
       <c r="B34" s="1">
         <f t="shared" si="0"/>
-        <v>9722.9443403298719</v>
+        <v>4298.9469430080471</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1">
-        <v>1.097483641001932</v>
+      <c r="A35">
+        <v>0.47835733528780611</v>
       </c>
       <c r="B35" s="1">
         <f t="shared" si="0"/>
-        <v>9182.2406527996354</v>
+        <v>4002.2393104963526</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1">
-        <v>1.036485931463285</v>
+      <c r="A36">
+        <v>0.44534825262679101</v>
       </c>
       <c r="B36" s="1">
         <f t="shared" si="0"/>
-        <v>8671.8953252445954</v>
+        <v>3726.0644962231413</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1">
-        <v>0.97890927897724589</v>
+      <c r="A37">
+        <v>0.41462260145951291</v>
       </c>
       <c r="B37" s="1">
         <f t="shared" si="0"/>
-        <v>8190.1727196786742</v>
+        <v>3468.9943106718065</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1">
-        <v>0.92455849759321274</v>
+      <c r="A38">
+        <v>0.38602167165043971</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="0"/>
-        <v>7735.4397872767995</v>
+        <v>3229.7008847023899</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1">
-        <v>0.87324989433937361</v>
+      <c r="A39">
+        <v>0.35939788503072623</v>
       </c>
       <c r="B39" s="1">
         <f t="shared" si="0"/>
-        <v>7306.1596367265283</v>
+        <v>3006.9494862325105</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1">
-        <v>0.82481055387745528</v>
+      <c r="A40">
+        <v>0.33461400082231779</v>
       </c>
       <c r="B40" s="1">
         <f t="shared" si="0"/>
-        <v>6900.8855491982877</v>
+        <v>2799.5918723140294</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1">
-        <v>0.77907767203677736</v>
+      <c r="A41">
+        <v>0.31154237978937732</v>
       </c>
       <c r="B41" s="1">
         <f t="shared" si="0"/>
-        <v>6518.2554022707354</v>
+        <v>2606.5601325595776</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1">
-        <v>0.73589793429146277</v>
+      <c r="A42">
+        <v>0.29006430241437431</v>
       </c>
       <c r="B42" s="1">
         <f t="shared" si="0"/>
-        <v>6156.9864698789152</v>
+        <v>2426.8609845734791</v>
       </c>
     </row>
   </sheetData>
